--- a/tests/eindhoven-500/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaalproduct_Auto_OV_Fiets.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaalproduct_Auto_OV_Fiets.xlsx
@@ -388,10 +388,10 @@
         <v>355604</v>
       </c>
       <c r="C2">
-        <v>520718</v>
+        <v>520738</v>
       </c>
       <c r="D2">
-        <v>1006588</v>
+        <v>1006647</v>
       </c>
       <c r="E2">
         <v>1441912</v>
@@ -405,10 +405,10 @@
         <v>151395</v>
       </c>
       <c r="C3">
-        <v>263789</v>
+        <v>263793</v>
       </c>
       <c r="D3">
-        <v>530867</v>
+        <v>530896</v>
       </c>
       <c r="E3">
         <v>663981</v>
@@ -425,10 +425,10 @@
         <v>22636</v>
       </c>
       <c r="D4">
-        <v>49141</v>
+        <v>49143</v>
       </c>
       <c r="E4">
-        <v>69931</v>
+        <v>69942</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -439,13 +439,13 @@
         <v>467034</v>
       </c>
       <c r="C5">
-        <v>701713</v>
+        <v>701714</v>
       </c>
       <c r="D5">
-        <v>1523381</v>
+        <v>1523445</v>
       </c>
       <c r="E5">
-        <v>2307737</v>
+        <v>2308080</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -456,13 +456,13 @@
         <v>750085</v>
       </c>
       <c r="C6">
-        <v>928072</v>
+        <v>928073</v>
       </c>
       <c r="D6">
-        <v>2162218</v>
+        <v>2162309</v>
       </c>
       <c r="E6">
-        <v>4405679</v>
+        <v>4406334</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -473,13 +473,13 @@
         <v>1026841</v>
       </c>
       <c r="C7">
-        <v>1189031</v>
+        <v>1189708</v>
       </c>
       <c r="D7">
-        <v>2642365</v>
+        <v>2643672</v>
       </c>
       <c r="E7">
-        <v>5489480</v>
+        <v>5493119</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -490,13 +490,13 @@
         <v>3514399</v>
       </c>
       <c r="C8">
-        <v>4968452</v>
+        <v>4971279</v>
       </c>
       <c r="D8">
-        <v>8509312</v>
+        <v>8513519</v>
       </c>
       <c r="E8">
-        <v>8266511</v>
+        <v>8271991</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -507,13 +507,13 @@
         <v>1857636</v>
       </c>
       <c r="C9">
-        <v>2813531</v>
+        <v>2816809</v>
       </c>
       <c r="D9">
-        <v>4255847</v>
+        <v>4262134</v>
       </c>
       <c r="E9">
-        <v>2758835</v>
+        <v>2764833</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -524,13 +524,13 @@
         <v>1301629</v>
       </c>
       <c r="C10">
-        <v>2781484</v>
+        <v>2783066</v>
       </c>
       <c r="D10">
-        <v>4120299</v>
+        <v>4122336</v>
       </c>
       <c r="E10">
-        <v>1743717</v>
+        <v>1744873</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -541,13 +541,13 @@
         <v>1157004</v>
       </c>
       <c r="C11">
-        <v>1868478</v>
+        <v>1869541</v>
       </c>
       <c r="D11">
-        <v>2866295</v>
+        <v>2867712</v>
       </c>
       <c r="E11">
-        <v>1872881</v>
+        <v>1874123</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -558,10 +558,10 @@
         <v>418019</v>
       </c>
       <c r="C12">
-        <v>475034</v>
+        <v>475035</v>
       </c>
       <c r="D12">
-        <v>1181203</v>
+        <v>1181251</v>
       </c>
       <c r="E12">
         <v>3166515</v>
@@ -575,10 +575,10 @@
         <v>1698989</v>
       </c>
       <c r="C13">
-        <v>3112713</v>
+        <v>3112759</v>
       </c>
       <c r="D13">
-        <v>6742013</v>
+        <v>6742380</v>
       </c>
       <c r="E13">
         <v>9295727</v>
@@ -592,10 +592,10 @@
         <v>498926</v>
       </c>
       <c r="C14">
-        <v>1101216</v>
+        <v>1101218</v>
       </c>
       <c r="D14">
-        <v>3118375</v>
+        <v>3118503</v>
       </c>
       <c r="E14">
         <v>5851169</v>
@@ -609,13 +609,13 @@
         <v>1706580</v>
       </c>
       <c r="C15">
-        <v>2378063</v>
+        <v>2379415</v>
       </c>
       <c r="D15">
-        <v>5060801</v>
+        <v>5063303</v>
       </c>
       <c r="E15">
-        <v>7749854</v>
+        <v>7754992</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -626,13 +626,13 @@
         <v>3534016</v>
       </c>
       <c r="C16">
-        <v>5315631</v>
+        <v>5316622</v>
       </c>
       <c r="D16">
-        <v>9964598</v>
+        <v>9970928</v>
       </c>
       <c r="E16">
-        <v>10946757</v>
+        <v>10952462</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -643,10 +643,10 @@
         <v>1011337</v>
       </c>
       <c r="C17">
-        <v>1662620</v>
+        <v>1662624</v>
       </c>
       <c r="D17">
-        <v>3401864</v>
+        <v>3402004</v>
       </c>
       <c r="E17">
         <v>4336749</v>
@@ -660,10 +660,10 @@
         <v>1059766</v>
       </c>
       <c r="C18">
-        <v>1688251</v>
+        <v>1688276</v>
       </c>
       <c r="D18">
-        <v>3875330</v>
+        <v>3875541</v>
       </c>
       <c r="E18">
         <v>7008683</v>
@@ -677,13 +677,13 @@
         <v>2185697</v>
       </c>
       <c r="C19">
-        <v>3212744</v>
+        <v>3213343</v>
       </c>
       <c r="D19">
-        <v>6535485</v>
+        <v>6539637</v>
       </c>
       <c r="E19">
-        <v>8698234</v>
+        <v>8702767</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -694,13 +694,13 @@
         <v>1717333</v>
       </c>
       <c r="C20">
-        <v>2453368</v>
+        <v>2453826</v>
       </c>
       <c r="D20">
-        <v>5163840</v>
+        <v>5167121</v>
       </c>
       <c r="E20">
-        <v>7573972</v>
+        <v>7577920</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -711,13 +711,13 @@
         <v>1930226</v>
       </c>
       <c r="C21">
-        <v>2648080</v>
+        <v>2648574</v>
       </c>
       <c r="D21">
-        <v>4155278</v>
+        <v>4157918</v>
       </c>
       <c r="E21">
-        <v>3372785</v>
+        <v>3374542</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -728,13 +728,13 @@
         <v>876086</v>
       </c>
       <c r="C22">
-        <v>1205013</v>
+        <v>1205216</v>
       </c>
       <c r="D22">
-        <v>2542926</v>
+        <v>2543312</v>
       </c>
       <c r="E22">
-        <v>4994510</v>
+        <v>4995729</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -745,10 +745,10 @@
         <v>210129</v>
       </c>
       <c r="C23">
-        <v>473380</v>
+        <v>473398</v>
       </c>
       <c r="D23">
-        <v>958655</v>
+        <v>958711</v>
       </c>
       <c r="E23">
         <v>961275</v>
@@ -762,13 +762,13 @@
         <v>2434567</v>
       </c>
       <c r="C24">
-        <v>4160438</v>
+        <v>4160456</v>
       </c>
       <c r="D24">
-        <v>8649250</v>
+        <v>8649605</v>
       </c>
       <c r="E24">
-        <v>9978414</v>
+        <v>9979416</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -779,13 +779,13 @@
         <v>1585819</v>
       </c>
       <c r="C25">
-        <v>2530933</v>
+        <v>2530944</v>
       </c>
       <c r="D25">
-        <v>5739957</v>
+        <v>5740193</v>
       </c>
       <c r="E25">
-        <v>8493531</v>
+        <v>8494384</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -799,10 +799,10 @@
         <v>17335</v>
       </c>
       <c r="D26">
-        <v>39315</v>
+        <v>39316</v>
       </c>
       <c r="E26">
-        <v>59395</v>
+        <v>59401</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -816,10 +816,10 @@
         <v>2097539</v>
       </c>
       <c r="D27">
-        <v>4478853</v>
+        <v>4479179</v>
       </c>
       <c r="E27">
-        <v>6183501</v>
+        <v>6184398</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -833,10 +833,10 @@
         <v>1455939</v>
       </c>
       <c r="D28">
-        <v>2951971</v>
+        <v>2952186</v>
       </c>
       <c r="E28">
-        <v>3411587</v>
+        <v>3412082</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -847,13 +847,13 @@
         <v>526494</v>
       </c>
       <c r="C29">
-        <v>913046</v>
+        <v>913047</v>
       </c>
       <c r="D29">
-        <v>1272401</v>
+        <v>1272494</v>
       </c>
       <c r="E29">
-        <v>568598</v>
+        <v>568680</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -864,13 +864,13 @@
         <v>4969909</v>
       </c>
       <c r="C30">
-        <v>7698594</v>
+        <v>7705562</v>
       </c>
       <c r="D30">
-        <v>9008035</v>
+        <v>9033797</v>
       </c>
       <c r="E30">
-        <v>5834882</v>
+        <v>5847159</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -881,13 +881,13 @@
         <v>7839439</v>
       </c>
       <c r="C31">
-        <v>12415870</v>
+        <v>12427107</v>
       </c>
       <c r="D31">
-        <v>15363398</v>
+        <v>15407335</v>
       </c>
       <c r="E31">
-        <v>11044598</v>
+        <v>11067836</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -898,13 +898,13 @@
         <v>4851944</v>
       </c>
       <c r="C32">
-        <v>5908418</v>
+        <v>5911430</v>
       </c>
       <c r="D32">
-        <v>10282344</v>
+        <v>10294955</v>
       </c>
       <c r="E32">
-        <v>19829331</v>
+        <v>19842462</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -915,13 +915,13 @@
         <v>6715293</v>
       </c>
       <c r="C33">
-        <v>9132646</v>
+        <v>9140911</v>
       </c>
       <c r="D33">
-        <v>13594949</v>
+        <v>13633829</v>
       </c>
       <c r="E33">
-        <v>16462703</v>
+        <v>16497340</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -929,16 +929,16 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>615179</v>
+        <v>615327</v>
       </c>
       <c r="C34">
-        <v>517225</v>
+        <v>517385</v>
       </c>
       <c r="D34">
-        <v>992217</v>
+        <v>992387</v>
       </c>
       <c r="E34">
-        <v>4272440</v>
+        <v>4272987</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -949,10 +949,10 @@
         <v>2543900</v>
       </c>
       <c r="C35">
-        <v>3216583</v>
+        <v>3216944</v>
       </c>
       <c r="D35">
-        <v>5081400</v>
+        <v>5082415</v>
       </c>
       <c r="E35">
         <v>8159722</v>
@@ -966,13 +966,13 @@
         <v>11516851</v>
       </c>
       <c r="C36">
-        <v>17820759</v>
+        <v>17822352</v>
       </c>
       <c r="D36">
-        <v>30604470</v>
+        <v>30622241</v>
       </c>
       <c r="E36">
-        <v>40843163</v>
+        <v>40867409</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -983,13 +983,13 @@
         <v>17217541</v>
       </c>
       <c r="C37">
-        <v>26497309</v>
+        <v>26503413</v>
       </c>
       <c r="D37">
-        <v>31524035</v>
+        <v>31588614</v>
       </c>
       <c r="E37">
-        <v>21447468</v>
+        <v>21488590</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1000,13 +1000,13 @@
         <v>18217856</v>
       </c>
       <c r="C38">
-        <v>22397439</v>
+        <v>22402598</v>
       </c>
       <c r="D38">
-        <v>30427547</v>
+        <v>30489880</v>
       </c>
       <c r="E38">
-        <v>34370942</v>
+        <v>34436843</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1014,16 +1014,16 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>841689</v>
+        <v>842102</v>
       </c>
       <c r="C39">
-        <v>1732322</v>
+        <v>1734856</v>
       </c>
       <c r="D39">
-        <v>1658738</v>
+        <v>1660455</v>
       </c>
       <c r="E39">
-        <v>541097</v>
+        <v>541390</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1034,13 +1034,13 @@
         <v>125168</v>
       </c>
       <c r="C40">
-        <v>157201</v>
+        <v>157215</v>
       </c>
       <c r="D40">
-        <v>214364</v>
+        <v>214404</v>
       </c>
       <c r="E40">
-        <v>252184</v>
+        <v>252213</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1051,10 +1051,10 @@
         <v>40379</v>
       </c>
       <c r="C41">
-        <v>51057</v>
+        <v>51063</v>
       </c>
       <c r="D41">
-        <v>69608</v>
+        <v>69622</v>
       </c>
       <c r="E41">
         <v>83262</v>
@@ -1068,13 +1068,13 @@
         <v>13791597</v>
       </c>
       <c r="C42">
-        <v>14403580</v>
+        <v>14404529</v>
       </c>
       <c r="D42">
-        <v>26137209</v>
+        <v>26156954</v>
       </c>
       <c r="E42">
-        <v>61440198</v>
+        <v>61480364</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1085,10 +1085,10 @@
         <v>16170541</v>
       </c>
       <c r="C43">
-        <v>15983713</v>
+        <v>15984209</v>
       </c>
       <c r="D43">
-        <v>28578430</v>
+        <v>28583255</v>
       </c>
       <c r="E43">
         <v>74753235</v>
@@ -1102,13 +1102,13 @@
         <v>6396610</v>
       </c>
       <c r="C44">
-        <v>7437533</v>
+        <v>7438343</v>
       </c>
       <c r="D44">
-        <v>11067672</v>
+        <v>11070542</v>
       </c>
       <c r="E44">
-        <v>16354989</v>
+        <v>16358714</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1119,13 +1119,13 @@
         <v>3505721</v>
       </c>
       <c r="C45">
-        <v>5922335</v>
+        <v>5922511</v>
       </c>
       <c r="D45">
-        <v>11020258</v>
+        <v>11027878</v>
       </c>
       <c r="E45">
-        <v>15861652</v>
+        <v>15870614</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1136,13 +1136,13 @@
         <v>6007247</v>
       </c>
       <c r="C46">
-        <v>8420978</v>
+        <v>8422192</v>
       </c>
       <c r="D46">
-        <v>12982636</v>
+        <v>12994739</v>
       </c>
       <c r="E46">
-        <v>16601206</v>
+        <v>16611312</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1153,13 +1153,13 @@
         <v>1426490</v>
       </c>
       <c r="C47">
-        <v>2323701</v>
+        <v>2323767</v>
       </c>
       <c r="D47">
-        <v>5099990</v>
+        <v>5100559</v>
       </c>
       <c r="E47">
-        <v>13575713</v>
+        <v>13577940</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1170,10 +1170,10 @@
         <v>1517318</v>
       </c>
       <c r="C48">
-        <v>1906691</v>
+        <v>1906716</v>
       </c>
       <c r="D48">
-        <v>3350789</v>
+        <v>3351138</v>
       </c>
       <c r="E48">
         <v>6271183</v>
@@ -1187,13 +1187,13 @@
         <v>12849639</v>
       </c>
       <c r="C49">
-        <v>17491172</v>
+        <v>17506050</v>
       </c>
       <c r="D49">
-        <v>29008804</v>
+        <v>29027059</v>
       </c>
       <c r="E49">
-        <v>30281412</v>
+        <v>30292224</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1207,7 +1207,7 @@
         <v>8715162</v>
       </c>
       <c r="D50">
-        <v>15429806</v>
+        <v>15430340</v>
       </c>
       <c r="E50">
         <v>19053066</v>
@@ -1221,10 +1221,10 @@
         <v>3706662</v>
       </c>
       <c r="C51">
-        <v>5449627</v>
+        <v>5449927</v>
       </c>
       <c r="D51">
-        <v>9872728</v>
+        <v>9873414</v>
       </c>
       <c r="E51">
         <v>11604934</v>
@@ -1238,10 +1238,10 @@
         <v>1840250</v>
       </c>
       <c r="C52">
-        <v>2432895</v>
+        <v>2433399</v>
       </c>
       <c r="D52">
-        <v>5331885</v>
+        <v>5332346</v>
       </c>
       <c r="E52">
         <v>10239710</v>
@@ -1255,13 +1255,13 @@
         <v>7890158</v>
       </c>
       <c r="C53">
-        <v>11585649</v>
+        <v>11586694</v>
       </c>
       <c r="D53">
-        <v>18848954</v>
+        <v>18859820</v>
       </c>
       <c r="E53">
-        <v>16737132</v>
+        <v>16742502</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1272,13 +1272,13 @@
         <v>8053220</v>
       </c>
       <c r="C54">
-        <v>12592637</v>
+        <v>12596741</v>
       </c>
       <c r="D54">
-        <v>25372748</v>
+        <v>25388338</v>
       </c>
       <c r="E54">
-        <v>32341941</v>
+        <v>32353564</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1292,7 +1292,7 @@
         <v>2605790</v>
       </c>
       <c r="D55">
-        <v>5507642</v>
+        <v>5507832</v>
       </c>
       <c r="E55">
         <v>7214268</v>
@@ -1306,10 +1306,10 @@
         <v>1094203</v>
       </c>
       <c r="C56">
-        <v>1361369</v>
+        <v>1361784</v>
       </c>
       <c r="D56">
-        <v>2926691</v>
+        <v>2926897</v>
       </c>
       <c r="E56">
         <v>6231682</v>
@@ -1323,13 +1323,13 @@
         <v>6379581</v>
       </c>
       <c r="C57">
-        <v>9207965</v>
+        <v>9208178</v>
       </c>
       <c r="D57">
-        <v>20502005</v>
+        <v>20503193</v>
       </c>
       <c r="E57">
-        <v>34950937</v>
+        <v>34953627</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1343,10 +1343,10 @@
         <v>3929395</v>
       </c>
       <c r="D58">
-        <v>8504487</v>
+        <v>8504806</v>
       </c>
       <c r="E58">
-        <v>13129155</v>
+        <v>13130493</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1360,10 +1360,10 @@
         <v>766711</v>
       </c>
       <c r="D59">
-        <v>1681678</v>
+        <v>1681741</v>
       </c>
       <c r="E59">
-        <v>2940384</v>
+        <v>2940683</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1374,13 +1374,13 @@
         <v>3634898</v>
       </c>
       <c r="C60">
-        <v>6351867</v>
+        <v>6351868</v>
       </c>
       <c r="D60">
-        <v>13193370</v>
+        <v>13193732</v>
       </c>
       <c r="E60">
-        <v>13998318</v>
+        <v>13999489</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1391,13 +1391,13 @@
         <v>1112724</v>
       </c>
       <c r="C61">
-        <v>1803419</v>
+        <v>1803420</v>
       </c>
       <c r="D61">
-        <v>4471703</v>
+        <v>4471825</v>
       </c>
       <c r="E61">
-        <v>7254189</v>
+        <v>7254796</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1408,13 +1408,13 @@
         <v>1186637</v>
       </c>
       <c r="C62">
-        <v>2418138</v>
+        <v>2418141</v>
       </c>
       <c r="D62">
-        <v>6565693</v>
+        <v>6565869</v>
       </c>
       <c r="E62">
-        <v>8524806</v>
+        <v>8525337</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1425,13 +1425,13 @@
         <v>444258</v>
       </c>
       <c r="C63">
-        <v>857340</v>
+        <v>857341</v>
       </c>
       <c r="D63">
-        <v>2542597</v>
+        <v>2542665</v>
       </c>
       <c r="E63">
-        <v>4182979</v>
+        <v>4183240</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1442,13 +1442,13 @@
         <v>428593</v>
       </c>
       <c r="C64">
-        <v>958001</v>
+        <v>958018</v>
       </c>
       <c r="D64">
-        <v>3083776</v>
+        <v>3083859</v>
       </c>
       <c r="E64">
-        <v>5052215</v>
+        <v>5052502</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1459,13 +1459,13 @@
         <v>135345</v>
       </c>
       <c r="C65">
-        <v>210760</v>
+        <v>210764</v>
       </c>
       <c r="D65">
-        <v>725594</v>
+        <v>725614</v>
       </c>
       <c r="E65">
-        <v>2020886</v>
+        <v>2021001</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1476,13 +1476,13 @@
         <v>7100264</v>
       </c>
       <c r="C66">
-        <v>11643386</v>
+        <v>11647431</v>
       </c>
       <c r="D66">
-        <v>20769930</v>
+        <v>20788502</v>
       </c>
       <c r="E66">
-        <v>25901940</v>
+        <v>25922842</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1493,10 +1493,10 @@
         <v>1994281</v>
       </c>
       <c r="C67">
-        <v>2430676</v>
+        <v>2430780</v>
       </c>
       <c r="D67">
-        <v>5286200</v>
+        <v>5286776</v>
       </c>
       <c r="E67">
         <v>15368222</v>
@@ -1510,13 +1510,13 @@
         <v>5068853</v>
       </c>
       <c r="C68">
-        <v>9278323</v>
+        <v>9281546</v>
       </c>
       <c r="D68">
-        <v>15051456</v>
+        <v>15064914</v>
       </c>
       <c r="E68">
-        <v>13968797</v>
+        <v>13980070</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1527,10 +1527,10 @@
         <v>5372828</v>
       </c>
       <c r="C69">
-        <v>9236570</v>
+        <v>9236966</v>
       </c>
       <c r="D69">
-        <v>15612729</v>
+        <v>15614432</v>
       </c>
       <c r="E69">
         <v>19404321</v>
@@ -1544,10 +1544,10 @@
         <v>2791993</v>
       </c>
       <c r="C70">
-        <v>4450007</v>
+        <v>4450198</v>
       </c>
       <c r="D70">
-        <v>7806365</v>
+        <v>7807216</v>
       </c>
       <c r="E70">
         <v>11332123</v>
@@ -1561,13 +1561,13 @@
         <v>327944</v>
       </c>
       <c r="C71">
-        <v>548361</v>
+        <v>548373</v>
       </c>
       <c r="D71">
-        <v>860402</v>
+        <v>860519</v>
       </c>
       <c r="E71">
-        <v>1128459</v>
+        <v>1128677</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1578,13 +1578,13 @@
         <v>592975</v>
       </c>
       <c r="C72">
-        <v>858460</v>
+        <v>858481</v>
       </c>
       <c r="D72">
-        <v>1333167</v>
+        <v>1333310</v>
       </c>
       <c r="E72">
-        <v>1648888</v>
+        <v>1649239</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1595,13 +1595,13 @@
         <v>1136536</v>
       </c>
       <c r="C73">
-        <v>1794962</v>
+        <v>1795006</v>
       </c>
       <c r="D73">
-        <v>3301175</v>
+        <v>3301530</v>
       </c>
       <c r="E73">
-        <v>5339258</v>
+        <v>5340394</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1612,13 +1612,13 @@
         <v>444731</v>
       </c>
       <c r="C74">
-        <v>663356</v>
+        <v>663372</v>
       </c>
       <c r="D74">
-        <v>1206199</v>
+        <v>1206328</v>
       </c>
       <c r="E74">
-        <v>1805925</v>
+        <v>1806310</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1632,10 +1632,10 @@
         <v>1295236</v>
       </c>
       <c r="D75">
-        <v>2682885</v>
+        <v>2682970</v>
       </c>
       <c r="E75">
-        <v>4952931</v>
+        <v>4953662</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1646,10 +1646,10 @@
         <v>2768531</v>
       </c>
       <c r="C76">
-        <v>5347488</v>
+        <v>5347717</v>
       </c>
       <c r="D76">
-        <v>10265062</v>
+        <v>10266181</v>
       </c>
       <c r="E76">
         <v>14747284</v>
@@ -1663,13 +1663,13 @@
         <v>4694969</v>
       </c>
       <c r="C77">
-        <v>7933873</v>
+        <v>7933912</v>
       </c>
       <c r="D77">
-        <v>13917241</v>
+        <v>13918453</v>
       </c>
       <c r="E77">
-        <v>18040653</v>
+        <v>18045168</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1680,13 +1680,13 @@
         <v>934436</v>
       </c>
       <c r="C78">
-        <v>1505967</v>
+        <v>1505974</v>
       </c>
       <c r="D78">
-        <v>2659739</v>
+        <v>2659971</v>
       </c>
       <c r="E78">
-        <v>3561674</v>
+        <v>3562565</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1697,13 +1697,13 @@
         <v>113956</v>
       </c>
       <c r="C79">
-        <v>183654</v>
+        <v>183655</v>
       </c>
       <c r="D79">
-        <v>371126</v>
+        <v>371159</v>
       </c>
       <c r="E79">
-        <v>464566</v>
+        <v>464682</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -1714,13 +1714,13 @@
         <v>683733</v>
       </c>
       <c r="C80">
-        <v>808080</v>
+        <v>808084</v>
       </c>
       <c r="D80">
-        <v>1360797</v>
+        <v>1360915</v>
       </c>
       <c r="E80">
-        <v>2555114</v>
+        <v>2555753</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -1731,13 +1731,13 @@
         <v>5569414</v>
       </c>
       <c r="C81">
-        <v>8194963</v>
+        <v>8195040</v>
       </c>
       <c r="D81">
-        <v>13311330</v>
+        <v>13312698</v>
       </c>
       <c r="E81">
-        <v>18586909</v>
+        <v>18590185</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -1748,13 +1748,13 @@
         <v>659102</v>
       </c>
       <c r="C82">
-        <v>773969</v>
+        <v>773976</v>
       </c>
       <c r="D82">
-        <v>1264576</v>
+        <v>1264706</v>
       </c>
       <c r="E82">
-        <v>2163132</v>
+        <v>2163513</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -1765,13 +1765,13 @@
         <v>5332129</v>
       </c>
       <c r="C83">
-        <v>8082170</v>
+        <v>8082182</v>
       </c>
       <c r="D83">
-        <v>14001959</v>
+        <v>14003155</v>
       </c>
       <c r="E83">
-        <v>19097162</v>
+        <v>19101766</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -1782,13 +1782,13 @@
         <v>1205525</v>
       </c>
       <c r="C84">
-        <v>1694079</v>
+        <v>1694082</v>
       </c>
       <c r="D84">
-        <v>3267124</v>
+        <v>3267403</v>
       </c>
       <c r="E84">
-        <v>6049864</v>
+        <v>6051323</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -1799,13 +1799,13 @@
         <v>6215826</v>
       </c>
       <c r="C85">
-        <v>9628065</v>
+        <v>9628236</v>
       </c>
       <c r="D85">
-        <v>14228730</v>
+        <v>14231772</v>
       </c>
       <c r="E85">
-        <v>16049686</v>
+        <v>16053202</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -1816,13 +1816,13 @@
         <v>3198788</v>
       </c>
       <c r="C86">
-        <v>4036007</v>
+        <v>4036079</v>
       </c>
       <c r="D86">
-        <v>5991044</v>
+        <v>5992325</v>
       </c>
       <c r="E86">
-        <v>8586582</v>
+        <v>8588463</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -1833,13 +1833,13 @@
         <v>3551416</v>
       </c>
       <c r="C87">
-        <v>5848278</v>
+        <v>5849292</v>
       </c>
       <c r="D87">
-        <v>9844837</v>
+        <v>9847393</v>
       </c>
       <c r="E87">
-        <v>14048715</v>
+        <v>14051937</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -1850,13 +1850,13 @@
         <v>765992</v>
       </c>
       <c r="C88">
-        <v>724993</v>
+        <v>725119</v>
       </c>
       <c r="D88">
-        <v>1376900</v>
+        <v>1377258</v>
       </c>
       <c r="E88">
-        <v>4791180</v>
+        <v>4792279</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -1867,13 +1867,13 @@
         <v>1601619</v>
       </c>
       <c r="C89">
-        <v>1788316</v>
+        <v>1788627</v>
       </c>
       <c r="D89">
-        <v>2616111</v>
+        <v>2616790</v>
       </c>
       <c r="E89">
-        <v>3897909</v>
+        <v>3898803</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -1881,16 +1881,16 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>31196269</v>
+        <v>31196750</v>
       </c>
       <c r="C90">
-        <v>33502355</v>
+        <v>33542755</v>
       </c>
       <c r="D90">
-        <v>45075167</v>
+        <v>45336146</v>
       </c>
       <c r="E90">
-        <v>65970076</v>
+        <v>66636793</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -1898,16 +1898,16 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>18522431</v>
+        <v>18522720</v>
       </c>
       <c r="C91">
-        <v>20781567</v>
+        <v>20807563</v>
       </c>
       <c r="D91">
-        <v>31628916</v>
+        <v>31824088</v>
       </c>
       <c r="E91">
-        <v>57949984</v>
+        <v>58599916</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -1915,16 +1915,16 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>14851990</v>
+        <v>14852237</v>
       </c>
       <c r="C92">
-        <v>16233638</v>
+        <v>16257087</v>
       </c>
       <c r="D92">
-        <v>25752445</v>
+        <v>25953748</v>
       </c>
       <c r="E92">
-        <v>53688529</v>
+        <v>54551267</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -1932,16 +1932,16 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>1222379</v>
+        <v>1222395</v>
       </c>
       <c r="C93">
-        <v>1737370</v>
+        <v>1738865</v>
       </c>
       <c r="D93">
-        <v>2480010</v>
+        <v>2487205</v>
       </c>
       <c r="E93">
-        <v>3081466</v>
+        <v>3087197</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -1952,13 +1952,13 @@
         <v>6960986</v>
       </c>
       <c r="C94">
-        <v>8452071</v>
+        <v>8454744</v>
       </c>
       <c r="D94">
-        <v>6283146</v>
+        <v>6361819</v>
       </c>
       <c r="E94">
-        <v>2333471</v>
+        <v>2400144</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -1966,16 +1966,16 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>16246246</v>
+        <v>16246469</v>
       </c>
       <c r="C95">
-        <v>17882312</v>
+        <v>17898260</v>
       </c>
       <c r="D95">
-        <v>27096833</v>
+        <v>27182484</v>
       </c>
       <c r="E95">
-        <v>50687365</v>
+        <v>50818580</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -1983,16 +1983,16 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>14142060</v>
+        <v>14142290</v>
       </c>
       <c r="C96">
-        <v>15570492</v>
+        <v>15591958</v>
       </c>
       <c r="D96">
-        <v>19825885</v>
+        <v>19969722</v>
       </c>
       <c r="E96">
-        <v>25099814</v>
+        <v>25461292</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2000,16 +2000,16 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>5806298</v>
+        <v>5806377</v>
       </c>
       <c r="C97">
-        <v>4632986</v>
+        <v>4636973</v>
       </c>
       <c r="D97">
-        <v>7723458</v>
+        <v>7745868</v>
       </c>
       <c r="E97">
-        <v>25300460</v>
+        <v>25347510</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2017,16 +2017,16 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>16259626</v>
+        <v>16260190</v>
       </c>
       <c r="C98">
-        <v>16872134</v>
+        <v>16889142</v>
       </c>
       <c r="D98">
-        <v>25089818</v>
+        <v>25213047</v>
       </c>
       <c r="E98">
-        <v>46028272</v>
+        <v>46180238</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2034,16 +2034,16 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>8782632</v>
+        <v>8782954</v>
       </c>
       <c r="C99">
-        <v>10263770</v>
+        <v>10275844</v>
       </c>
       <c r="D99">
-        <v>13887000</v>
+        <v>13983021</v>
       </c>
       <c r="E99">
-        <v>18644765</v>
+        <v>18809356</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2054,13 +2054,13 @@
         <v>9736535</v>
       </c>
       <c r="C100">
-        <v>11543058</v>
+        <v>11556276</v>
       </c>
       <c r="D100">
-        <v>13441765</v>
+        <v>13497937</v>
       </c>
       <c r="E100">
-        <v>13252697</v>
+        <v>13317416</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2071,13 +2071,13 @@
         <v>3951330</v>
       </c>
       <c r="C101">
-        <v>4801217</v>
+        <v>4807294</v>
       </c>
       <c r="D101">
-        <v>7113238</v>
+        <v>7149776</v>
       </c>
       <c r="E101">
-        <v>11089361</v>
+        <v>11175639</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2088,13 +2088,13 @@
         <v>1639256</v>
       </c>
       <c r="C102">
-        <v>877493</v>
+        <v>878400</v>
       </c>
       <c r="D102">
-        <v>1427082</v>
+        <v>1431790</v>
       </c>
       <c r="E102">
-        <v>6701258</v>
+        <v>6716349</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2105,13 +2105,13 @@
         <v>15224196</v>
       </c>
       <c r="C103">
-        <v>18156905</v>
+        <v>18196971</v>
       </c>
       <c r="D103">
-        <v>19411439</v>
+        <v>19555898</v>
       </c>
       <c r="E103">
-        <v>15326089</v>
+        <v>15391093</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2122,13 +2122,13 @@
         <v>19874815</v>
       </c>
       <c r="C104">
-        <v>20574396</v>
+        <v>20619797</v>
       </c>
       <c r="D104">
-        <v>30409047</v>
+        <v>30635348</v>
       </c>
       <c r="E104">
-        <v>54309371</v>
+        <v>54539718</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2139,13 +2139,13 @@
         <v>5915721</v>
       </c>
       <c r="C105">
-        <v>6031556</v>
+        <v>6033994</v>
       </c>
       <c r="D105">
-        <v>8825598</v>
+        <v>8840099</v>
       </c>
       <c r="E105">
-        <v>15894601</v>
+        <v>15917668</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2156,13 +2156,13 @@
         <v>3383946</v>
       </c>
       <c r="C106">
-        <v>1914667</v>
+        <v>1916262</v>
       </c>
       <c r="D106">
-        <v>3459106</v>
+        <v>3462259</v>
       </c>
       <c r="E106">
-        <v>17596204</v>
+        <v>17604207</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2173,13 +2173,13 @@
         <v>8314838</v>
       </c>
       <c r="C107">
-        <v>6641502</v>
+        <v>6647035</v>
       </c>
       <c r="D107">
-        <v>11222878</v>
+        <v>11233106</v>
       </c>
       <c r="E107">
-        <v>36324837</v>
+        <v>36341358</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2190,10 +2190,10 @@
         <v>52387</v>
       </c>
       <c r="C108">
-        <v>65016</v>
+        <v>65017</v>
       </c>
       <c r="D108">
-        <v>80911</v>
+        <v>80918</v>
       </c>
       <c r="E108">
         <v>181716</v>
@@ -2204,16 +2204,16 @@
         <v>108</v>
       </c>
       <c r="B109">
-        <v>5585888</v>
+        <v>5586167</v>
       </c>
       <c r="C109">
-        <v>6710332</v>
+        <v>6725750</v>
       </c>
       <c r="D109">
-        <v>11867100</v>
+        <v>11895848</v>
       </c>
       <c r="E109">
-        <v>27842433</v>
+        <v>27887048</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2221,16 +2221,16 @@
         <v>109</v>
       </c>
       <c r="B110">
-        <v>43301</v>
+        <v>43304</v>
       </c>
       <c r="C110">
-        <v>53257</v>
+        <v>53379</v>
       </c>
       <c r="D110">
-        <v>69806</v>
+        <v>69976</v>
       </c>
       <c r="E110">
-        <v>81649</v>
+        <v>81780</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2238,16 +2238,16 @@
         <v>110</v>
       </c>
       <c r="B111">
-        <v>22049642</v>
+        <v>22050829</v>
       </c>
       <c r="C111">
-        <v>28796045</v>
+        <v>28877171</v>
       </c>
       <c r="D111">
-        <v>32634523</v>
+        <v>32775941</v>
       </c>
       <c r="E111">
-        <v>26954902</v>
+        <v>27105183</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2255,16 +2255,16 @@
         <v>111</v>
       </c>
       <c r="B112">
-        <v>11275129</v>
+        <v>11277520</v>
       </c>
       <c r="C112">
-        <v>13621942</v>
+        <v>13687628</v>
       </c>
       <c r="D112">
-        <v>18367040</v>
+        <v>18538804</v>
       </c>
       <c r="E112">
-        <v>23134604</v>
+        <v>23234989</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2275,13 +2275,13 @@
         <v>14017806</v>
       </c>
       <c r="C113">
-        <v>16968980</v>
+        <v>17001716</v>
       </c>
       <c r="D113">
-        <v>14153744</v>
+        <v>14190835</v>
       </c>
       <c r="E113">
-        <v>5092812</v>
+        <v>5102704</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2292,13 +2292,13 @@
         <v>9364671</v>
       </c>
       <c r="C114">
-        <v>9653633</v>
+        <v>9663049</v>
       </c>
       <c r="D114">
-        <v>16158138</v>
+        <v>16173137</v>
       </c>
       <c r="E114">
-        <v>37640077</v>
+        <v>37658192</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2306,16 +2306,16 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>8297929</v>
+        <v>8299713</v>
       </c>
       <c r="C115">
-        <v>10450477</v>
+        <v>10502986</v>
       </c>
       <c r="D115">
-        <v>10999250</v>
+        <v>11112643</v>
       </c>
       <c r="E115">
-        <v>8004345</v>
+        <v>8054367</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2323,16 +2323,16 @@
         <v>115</v>
       </c>
       <c r="B116">
-        <v>21020687</v>
+        <v>21025144</v>
       </c>
       <c r="C116">
-        <v>24251184</v>
+        <v>24368125</v>
       </c>
       <c r="D116">
-        <v>31543394</v>
+        <v>31838380</v>
       </c>
       <c r="E116">
-        <v>39005101</v>
+        <v>39174350</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2343,13 +2343,13 @@
         <v>2670915</v>
       </c>
       <c r="C117">
-        <v>2692081</v>
+        <v>2697208</v>
       </c>
       <c r="D117">
-        <v>4333849</v>
+        <v>4344718</v>
       </c>
       <c r="E117">
-        <v>9469882</v>
+        <v>9486004</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2360,13 +2360,13 @@
         <v>51365</v>
       </c>
       <c r="C118">
-        <v>64389</v>
+        <v>64397</v>
       </c>
       <c r="D118">
-        <v>81410</v>
+        <v>81418</v>
       </c>
       <c r="E118">
-        <v>90528</v>
+        <v>90534</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2377,10 +2377,10 @@
         <v>846135</v>
       </c>
       <c r="C119">
-        <v>535730</v>
+        <v>535789</v>
       </c>
       <c r="D119">
-        <v>844817</v>
+        <v>844902</v>
       </c>
       <c r="E119">
         <v>3080651</v>
@@ -2391,16 +2391,16 @@
         <v>119</v>
       </c>
       <c r="B120">
-        <v>13633355</v>
+        <v>13633858</v>
       </c>
       <c r="C120">
-        <v>11518740</v>
+        <v>11527951</v>
       </c>
       <c r="D120">
-        <v>19366286</v>
+        <v>19442878</v>
       </c>
       <c r="E120">
-        <v>59188371</v>
+        <v>59337904</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2408,16 +2408,16 @@
         <v>120</v>
       </c>
       <c r="B121">
-        <v>26974567</v>
+        <v>26975563</v>
       </c>
       <c r="C121">
-        <v>32319573</v>
+        <v>32345416</v>
       </c>
       <c r="D121">
-        <v>36511350</v>
+        <v>36655748</v>
       </c>
       <c r="E121">
-        <v>33524037</v>
+        <v>33608731</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2428,13 +2428,13 @@
         <v>27589055</v>
       </c>
       <c r="C122">
-        <v>34290718</v>
+        <v>34319363</v>
       </c>
       <c r="D122">
-        <v>37642606</v>
+        <v>37740061</v>
       </c>
       <c r="E122">
-        <v>30713488</v>
+        <v>30760104</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2445,13 +2445,13 @@
         <v>25957308</v>
       </c>
       <c r="C123">
-        <v>30829260</v>
+        <v>30857128</v>
       </c>
       <c r="D123">
-        <v>27793043</v>
+        <v>27885545</v>
       </c>
       <c r="E123">
-        <v>14638711</v>
+        <v>14680886</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2462,13 +2462,13 @@
         <v>8005349</v>
       </c>
       <c r="C124">
-        <v>8764401</v>
+        <v>8771722</v>
       </c>
       <c r="D124">
-        <v>15437698</v>
+        <v>15477665</v>
       </c>
       <c r="E124">
-        <v>39968486</v>
+        <v>40029148</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2479,13 +2479,13 @@
         <v>28185968</v>
       </c>
       <c r="C125">
-        <v>36524057</v>
+        <v>36564798</v>
       </c>
       <c r="D125">
-        <v>40647294</v>
+        <v>40751806</v>
       </c>
       <c r="E125">
-        <v>32619136</v>
+        <v>32670526</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2496,13 +2496,13 @@
         <v>1636445</v>
       </c>
       <c r="C126">
-        <v>1408056</v>
+        <v>1408943</v>
       </c>
       <c r="D126">
-        <v>1424910</v>
+        <v>1426257</v>
       </c>
       <c r="E126">
-        <v>1366139</v>
+        <v>1366755</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -2510,16 +2510,16 @@
         <v>126</v>
       </c>
       <c r="B127">
-        <v>30634274</v>
+        <v>30636420</v>
       </c>
       <c r="C127">
-        <v>35515397</v>
+        <v>35555261</v>
       </c>
       <c r="D127">
-        <v>38312620</v>
+        <v>38354591</v>
       </c>
       <c r="E127">
-        <v>32965305</v>
+        <v>32982231</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -2530,10 +2530,10 @@
         <v>2321500</v>
       </c>
       <c r="C128">
-        <v>908069</v>
+        <v>908166</v>
       </c>
       <c r="D128">
-        <v>1669052</v>
+        <v>1669244</v>
       </c>
       <c r="E128">
         <v>13448290</v>
@@ -2547,10 +2547,10 @@
         <v>2213523</v>
       </c>
       <c r="C129">
-        <v>2010724</v>
+        <v>2010939</v>
       </c>
       <c r="D129">
-        <v>3576539</v>
+        <v>3576952</v>
       </c>
       <c r="E129">
         <v>12193116</v>
@@ -2561,16 +2561,16 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <v>13453562</v>
+        <v>13453881</v>
       </c>
       <c r="C130">
-        <v>15081809</v>
+        <v>15092834</v>
       </c>
       <c r="D130">
-        <v>15228763</v>
+        <v>15283671</v>
       </c>
       <c r="E130">
-        <v>11880134</v>
+        <v>11915736</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -2578,16 +2578,16 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>23145857</v>
+        <v>23146493</v>
       </c>
       <c r="C131">
-        <v>27744995</v>
+        <v>27774692</v>
       </c>
       <c r="D131">
-        <v>27659025</v>
+        <v>27868340</v>
       </c>
       <c r="E131">
-        <v>19646455</v>
+        <v>19925775</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -2595,16 +2595,16 @@
         <v>131</v>
       </c>
       <c r="B132">
-        <v>40302790</v>
+        <v>40303887</v>
       </c>
       <c r="C132">
-        <v>41985154</v>
+        <v>42029024</v>
       </c>
       <c r="D132">
-        <v>38462953</v>
+        <v>38742425</v>
       </c>
       <c r="E132">
-        <v>25828661</v>
+        <v>26173335</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -2612,16 +2612,16 @@
         <v>132</v>
       </c>
       <c r="B133">
-        <v>14061248</v>
+        <v>14061612</v>
       </c>
       <c r="C133">
-        <v>14550982</v>
+        <v>14564423</v>
       </c>
       <c r="D133">
-        <v>15992464</v>
+        <v>16085897</v>
       </c>
       <c r="E133">
-        <v>16314755</v>
+        <v>16465952</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -2632,13 +2632,13 @@
         <v>6134193</v>
       </c>
       <c r="C134">
-        <v>7852533</v>
+        <v>7854063</v>
       </c>
       <c r="D134">
-        <v>13982813</v>
+        <v>14079677</v>
       </c>
       <c r="E134">
-        <v>35232805</v>
+        <v>35690899</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2649,13 +2649,13 @@
         <v>40140790</v>
       </c>
       <c r="C135">
-        <v>44923943</v>
+        <v>44960506</v>
       </c>
       <c r="D135">
-        <v>45969853</v>
+        <v>46165085</v>
       </c>
       <c r="E135">
-        <v>36861333</v>
+        <v>37004017</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -2666,13 +2666,13 @@
         <v>31155279</v>
       </c>
       <c r="C136">
-        <v>34973920</v>
+        <v>35012584</v>
       </c>
       <c r="D136">
-        <v>38997405</v>
+        <v>39237335</v>
       </c>
       <c r="E136">
-        <v>37079866</v>
+        <v>37305613</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -2683,13 +2683,13 @@
         <v>15749899</v>
       </c>
       <c r="C137">
-        <v>16578476</v>
+        <v>16595342</v>
       </c>
       <c r="D137">
-        <v>19515340</v>
+        <v>19614192</v>
       </c>
       <c r="E137">
-        <v>22128617</v>
+        <v>22198171</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -2700,13 +2700,13 @@
         <v>25093875</v>
       </c>
       <c r="C138">
-        <v>32831884</v>
+        <v>32865286</v>
       </c>
       <c r="D138">
-        <v>32748344</v>
+        <v>32914227</v>
       </c>
       <c r="E138">
-        <v>20959852</v>
+        <v>21025733</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -2717,13 +2717,13 @@
         <v>21305609</v>
       </c>
       <c r="C139">
-        <v>23558031</v>
+        <v>23586368</v>
       </c>
       <c r="D139">
-        <v>24057509</v>
+        <v>24167866</v>
       </c>
       <c r="E139">
-        <v>19313669</v>
+        <v>19367466</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -2734,10 +2734,10 @@
         <v>5405165</v>
       </c>
       <c r="C140">
-        <v>6293276</v>
+        <v>6297517</v>
       </c>
       <c r="D140">
-        <v>6133645</v>
+        <v>6140886</v>
       </c>
       <c r="E140">
         <v>5374393</v>
@@ -2751,13 +2751,13 @@
         <v>39400784</v>
       </c>
       <c r="C141">
-        <v>52069854</v>
+        <v>52132487</v>
       </c>
       <c r="D141">
-        <v>57085615</v>
+        <v>57347479</v>
       </c>
       <c r="E141">
-        <v>44539685</v>
+        <v>44663748</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -2768,13 +2768,13 @@
         <v>12500235</v>
       </c>
       <c r="C142">
-        <v>13692469</v>
+        <v>13709577</v>
       </c>
       <c r="D142">
-        <v>13966107</v>
+        <v>14036299</v>
       </c>
       <c r="E142">
-        <v>11224591</v>
+        <v>11268896</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -2785,13 +2785,13 @@
         <v>837234</v>
       </c>
       <c r="C143">
-        <v>918630</v>
+        <v>920406</v>
       </c>
       <c r="D143">
-        <v>855690</v>
+        <v>863798</v>
       </c>
       <c r="E143">
-        <v>529672</v>
+        <v>538180</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -2802,13 +2802,13 @@
         <v>20179471</v>
       </c>
       <c r="C144">
-        <v>27132826</v>
+        <v>27159569</v>
       </c>
       <c r="D144">
-        <v>31460084</v>
+        <v>31526752</v>
       </c>
       <c r="E144">
-        <v>27023188</v>
+        <v>27059381</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -2819,13 +2819,13 @@
         <v>6190892</v>
       </c>
       <c r="C145">
-        <v>6054432</v>
+        <v>6060400</v>
       </c>
       <c r="D145">
-        <v>10109645</v>
+        <v>10131069</v>
       </c>
       <c r="E145">
-        <v>25472008</v>
+        <v>25506123</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -2836,10 +2836,10 @@
         <v>2677555</v>
       </c>
       <c r="C146">
-        <v>3456316</v>
+        <v>3456811</v>
       </c>
       <c r="D146">
-        <v>3948775</v>
+        <v>3949783</v>
       </c>
       <c r="E146">
         <v>3605588</v>
@@ -2853,13 +2853,13 @@
         <v>4788240</v>
       </c>
       <c r="C147">
-        <v>4879558</v>
+        <v>4881663</v>
       </c>
       <c r="D147">
-        <v>7571835</v>
+        <v>7576893</v>
       </c>
       <c r="E147">
-        <v>15390592</v>
+        <v>15396139</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -2870,13 +2870,13 @@
         <v>32321593</v>
       </c>
       <c r="C148">
-        <v>41701024</v>
+        <v>41728358</v>
       </c>
       <c r="D148">
-        <v>46505294</v>
+        <v>46586252</v>
       </c>
       <c r="E148">
-        <v>37928794</v>
+        <v>37975621</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -2887,13 +2887,13 @@
         <v>27704657</v>
       </c>
       <c r="C149">
-        <v>33882164</v>
+        <v>33899195</v>
       </c>
       <c r="D149">
-        <v>29780908</v>
+        <v>29918669</v>
       </c>
       <c r="E149">
-        <v>14436648</v>
+        <v>14479131</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -2904,13 +2904,13 @@
         <v>16877550</v>
       </c>
       <c r="C150">
-        <v>17426573</v>
+        <v>17435333</v>
       </c>
       <c r="D150">
-        <v>18517616</v>
+        <v>18603275</v>
       </c>
       <c r="E150">
-        <v>17129495</v>
+        <v>17179902</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -2921,13 +2921,13 @@
         <v>4412864</v>
       </c>
       <c r="C151">
-        <v>6623680</v>
+        <v>6627471</v>
       </c>
       <c r="D151">
-        <v>8133475</v>
+        <v>8184084</v>
       </c>
       <c r="E151">
-        <v>6984553</v>
+        <v>7036214</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -2938,13 +2938,13 @@
         <v>27431705</v>
       </c>
       <c r="C152">
-        <v>30458175</v>
+        <v>30473485</v>
       </c>
       <c r="D152">
-        <v>28699123</v>
+        <v>28831880</v>
       </c>
       <c r="E152">
-        <v>18625520</v>
+        <v>18680330</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -2955,10 +2955,10 @@
         <v>670538</v>
       </c>
       <c r="C153">
-        <v>867679</v>
+        <v>867886</v>
       </c>
       <c r="D153">
-        <v>1255165</v>
+        <v>1255327</v>
       </c>
       <c r="E153">
         <v>1799971</v>
@@ -2972,10 +2972,10 @@
         <v>19445605</v>
       </c>
       <c r="C154">
-        <v>21055687</v>
+        <v>21060698</v>
       </c>
       <c r="D154">
-        <v>32560464</v>
+        <v>32564657</v>
       </c>
       <c r="E154">
         <v>62913261</v>
@@ -2989,13 +2989,13 @@
         <v>19934522</v>
       </c>
       <c r="C155">
-        <v>24452331</v>
+        <v>24474428</v>
       </c>
       <c r="D155">
-        <v>34520524</v>
+        <v>34598698</v>
       </c>
       <c r="E155">
-        <v>46469602</v>
+        <v>46535037</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3006,13 +3006,13 @@
         <v>21664377</v>
       </c>
       <c r="C156">
-        <v>30009679</v>
+        <v>30036798</v>
       </c>
       <c r="D156">
-        <v>45818149</v>
+        <v>45921908</v>
       </c>
       <c r="E156">
-        <v>64474705</v>
+        <v>64565494</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3023,13 +3023,13 @@
         <v>23406924</v>
       </c>
       <c r="C157">
-        <v>29957732</v>
+        <v>29975473</v>
       </c>
       <c r="D157">
-        <v>40960706</v>
+        <v>40997942</v>
       </c>
       <c r="E157">
-        <v>48875812</v>
+        <v>48895444</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3040,13 +3040,13 @@
         <v>35480336</v>
       </c>
       <c r="C158">
-        <v>40195094</v>
+        <v>40211823</v>
       </c>
       <c r="D158">
-        <v>45160072</v>
+        <v>45245034</v>
       </c>
       <c r="E158">
-        <v>41955678</v>
+        <v>42009565</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3057,13 +3057,13 @@
         <v>32305346</v>
       </c>
       <c r="C159">
-        <v>39214279</v>
+        <v>39238965</v>
       </c>
       <c r="D159">
-        <v>41636843</v>
+        <v>41859545</v>
       </c>
       <c r="E159">
-        <v>32317211</v>
+        <v>32419822</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3074,13 +3074,13 @@
         <v>9976411</v>
       </c>
       <c r="C160">
-        <v>9018578</v>
+        <v>9020466</v>
       </c>
       <c r="D160">
-        <v>14949189</v>
+        <v>14978271</v>
       </c>
       <c r="E160">
-        <v>38104552</v>
+        <v>38160010</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3091,13 +3091,13 @@
         <v>37048098</v>
       </c>
       <c r="C161">
-        <v>37999418</v>
+        <v>38023874</v>
       </c>
       <c r="D161">
-        <v>64060759</v>
+        <v>64115076</v>
       </c>
       <c r="E161">
-        <v>149057773</v>
+        <v>149124809</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3108,10 +3108,10 @@
         <v>508670</v>
       </c>
       <c r="C162">
-        <v>564407</v>
+        <v>564445</v>
       </c>
       <c r="D162">
-        <v>727420</v>
+        <v>727527</v>
       </c>
       <c r="E162">
         <v>1104016</v>
@@ -3125,13 +3125,13 @@
         <v>32341527</v>
       </c>
       <c r="C163">
-        <v>38065023</v>
+        <v>38090505</v>
       </c>
       <c r="D163">
-        <v>35072033</v>
+        <v>35275204</v>
       </c>
       <c r="E163">
-        <v>20038383</v>
+        <v>20101325</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3142,13 +3142,13 @@
         <v>3359793</v>
       </c>
       <c r="C164">
-        <v>2867980</v>
+        <v>2869206</v>
       </c>
       <c r="D164">
-        <v>5085051</v>
+        <v>5095318</v>
       </c>
       <c r="E164">
-        <v>17437628</v>
+        <v>17459464</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3159,13 +3159,13 @@
         <v>36494314</v>
       </c>
       <c r="C165">
-        <v>44074234</v>
+        <v>44081135</v>
       </c>
       <c r="D165">
-        <v>46007869</v>
+        <v>46110066</v>
       </c>
       <c r="E165">
-        <v>33611855</v>
+        <v>33659364</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3176,13 +3176,13 @@
         <v>11479046</v>
       </c>
       <c r="C166">
-        <v>16436118</v>
+        <v>16438692</v>
       </c>
       <c r="D166">
-        <v>25432128</v>
+        <v>25488620</v>
       </c>
       <c r="E166">
-        <v>35736306</v>
+        <v>35786818</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3193,13 +3193,13 @@
         <v>86769</v>
       </c>
       <c r="C167">
-        <v>105984</v>
+        <v>106093</v>
       </c>
       <c r="D167">
-        <v>70020</v>
+        <v>70084</v>
       </c>
       <c r="E167">
-        <v>81790</v>
+        <v>81827</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3210,13 +3210,13 @@
         <v>1006334</v>
       </c>
       <c r="C168">
-        <v>1244693</v>
+        <v>1244953</v>
       </c>
       <c r="D168">
-        <v>1453422</v>
+        <v>1453603</v>
       </c>
       <c r="E168">
-        <v>1310425</v>
+        <v>1310536</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3224,16 +3224,16 @@
         <v>168</v>
       </c>
       <c r="B169">
-        <v>19516000</v>
+        <v>19516029</v>
       </c>
       <c r="C169">
-        <v>21375869</v>
+        <v>21401332</v>
       </c>
       <c r="D169">
-        <v>32086418</v>
+        <v>32234058</v>
       </c>
       <c r="E169">
-        <v>58425087</v>
+        <v>58614929</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3244,13 +3244,13 @@
         <v>22870586</v>
       </c>
       <c r="C170">
-        <v>26415492</v>
+        <v>26424122</v>
       </c>
       <c r="D170">
-        <v>36989934</v>
+        <v>37140912</v>
       </c>
       <c r="E170">
-        <v>54732088</v>
+        <v>55111588</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3258,16 +3258,16 @@
         <v>170</v>
       </c>
       <c r="B171">
-        <v>4012702</v>
+        <v>4012708</v>
       </c>
       <c r="C171">
-        <v>4120271</v>
+        <v>4125054</v>
       </c>
       <c r="D171">
-        <v>6121049</v>
+        <v>6147516</v>
       </c>
       <c r="E171">
-        <v>11395591</v>
+        <v>11424526</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3278,13 +3278,13 @@
         <v>11359553</v>
       </c>
       <c r="C172">
-        <v>15236542</v>
+        <v>15240683</v>
       </c>
       <c r="D172">
-        <v>18482762</v>
+        <v>18532966</v>
       </c>
       <c r="E172">
-        <v>17489559</v>
+        <v>17527242</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3295,13 +3295,13 @@
         <v>26891626</v>
       </c>
       <c r="C173">
-        <v>32104383</v>
+        <v>32116324</v>
       </c>
       <c r="D173">
-        <v>39763630</v>
+        <v>39971194</v>
       </c>
       <c r="E173">
-        <v>44426778</v>
+        <v>44915214</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3312,13 +3312,13 @@
         <v>10840098</v>
       </c>
       <c r="C174">
-        <v>16556908</v>
+        <v>16558841</v>
       </c>
       <c r="D174">
-        <v>26817996</v>
+        <v>26974311</v>
       </c>
       <c r="E174">
-        <v>42590823</v>
+        <v>43198724</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3326,16 +3326,16 @@
         <v>174</v>
       </c>
       <c r="B175">
-        <v>502195</v>
+        <v>502199</v>
       </c>
       <c r="C175">
-        <v>538932</v>
+        <v>539167</v>
       </c>
       <c r="D175">
-        <v>682238</v>
+        <v>682731</v>
       </c>
       <c r="E175">
-        <v>862702</v>
+        <v>863037</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3343,16 +3343,16 @@
         <v>175</v>
       </c>
       <c r="B176">
-        <v>28793902</v>
+        <v>28794215</v>
       </c>
       <c r="C176">
-        <v>33932003</v>
+        <v>33955787</v>
       </c>
       <c r="D176">
-        <v>39999583</v>
+        <v>40075006</v>
       </c>
       <c r="E176">
-        <v>40136223</v>
+        <v>40190128</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3360,16 +3360,16 @@
         <v>176</v>
       </c>
       <c r="B177">
-        <v>24349523</v>
+        <v>24349788</v>
       </c>
       <c r="C177">
-        <v>31136945</v>
+        <v>31158770</v>
       </c>
       <c r="D177">
-        <v>36020939</v>
+        <v>36088860</v>
       </c>
       <c r="E177">
-        <v>32059529</v>
+        <v>32102587</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3380,13 +3380,13 @@
         <v>20677882</v>
       </c>
       <c r="C178">
-        <v>24649094</v>
+        <v>24662505</v>
       </c>
       <c r="D178">
-        <v>24206452</v>
+        <v>24334207</v>
       </c>
       <c r="E178">
-        <v>16286166</v>
+        <v>16343372</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3397,13 +3397,13 @@
         <v>3314193</v>
       </c>
       <c r="C179">
-        <v>2887514</v>
+        <v>2889140</v>
       </c>
       <c r="D179">
-        <v>6249138</v>
+        <v>6259234</v>
       </c>
       <c r="E179">
-        <v>50016379</v>
+        <v>50084196</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3414,13 +3414,13 @@
         <v>921596</v>
       </c>
       <c r="C180">
-        <v>1107980</v>
+        <v>1108027</v>
       </c>
       <c r="D180">
-        <v>1374214</v>
+        <v>1374328</v>
       </c>
       <c r="E180">
-        <v>1532478</v>
+        <v>1532575</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3431,13 +3431,13 @@
         <v>108423</v>
       </c>
       <c r="C181">
-        <v>65175</v>
+        <v>65178</v>
       </c>
       <c r="D181">
-        <v>80836</v>
+        <v>80843</v>
       </c>
       <c r="E181">
-        <v>180292</v>
+        <v>180303</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -3448,13 +3448,13 @@
         <v>146017</v>
       </c>
       <c r="C182">
-        <v>176795</v>
+        <v>176810</v>
       </c>
       <c r="D182">
-        <v>227298</v>
+        <v>227330</v>
       </c>
       <c r="E182">
-        <v>259871</v>
+        <v>259891</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -3468,10 +3468,10 @@
         <v>220325</v>
       </c>
       <c r="D183">
-        <v>361987</v>
+        <v>362035</v>
       </c>
       <c r="E183">
-        <v>1096583</v>
+        <v>1096669</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3482,13 +3482,13 @@
         <v>285264</v>
       </c>
       <c r="C184">
-        <v>284931</v>
+        <v>285034</v>
       </c>
       <c r="D184">
-        <v>440175</v>
+        <v>440554</v>
       </c>
       <c r="E184">
-        <v>1349925</v>
+        <v>1350499</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3499,13 +3499,13 @@
         <v>28764109</v>
       </c>
       <c r="C185">
-        <v>27182421</v>
+        <v>27192231</v>
       </c>
       <c r="D185">
-        <v>48712703</v>
+        <v>48754597</v>
       </c>
       <c r="E185">
-        <v>149504243</v>
+        <v>149567773</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -3516,10 +3516,10 @@
         <v>17129192</v>
       </c>
       <c r="C186">
-        <v>16921811</v>
+        <v>16922511</v>
       </c>
       <c r="D186">
-        <v>26526682</v>
+        <v>26529962</v>
       </c>
       <c r="E186">
         <v>57692124</v>
@@ -3533,13 +3533,13 @@
         <v>9559352</v>
       </c>
       <c r="C187">
-        <v>9672712</v>
+        <v>9675666</v>
       </c>
       <c r="D187">
-        <v>19098375</v>
+        <v>19114737</v>
       </c>
       <c r="E187">
-        <v>71957543</v>
+        <v>71988478</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -3550,10 +3550,10 @@
         <v>93872</v>
       </c>
       <c r="C188">
-        <v>114572</v>
+        <v>114587</v>
       </c>
       <c r="D188">
-        <v>147903</v>
+        <v>147926</v>
       </c>
       <c r="E188">
         <v>430006</v>
@@ -3567,13 +3567,13 @@
         <v>48116</v>
       </c>
       <c r="C189">
-        <v>58538</v>
+        <v>58544</v>
       </c>
       <c r="D189">
-        <v>75710</v>
+        <v>75721</v>
       </c>
       <c r="E189">
-        <v>86680</v>
+        <v>86687</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -3584,13 +3584,13 @@
         <v>48116</v>
       </c>
       <c r="C190">
-        <v>58538</v>
+        <v>58544</v>
       </c>
       <c r="D190">
-        <v>75710</v>
+        <v>75721</v>
       </c>
       <c r="E190">
-        <v>173360</v>
+        <v>173374</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -3598,16 +3598,16 @@
         <v>190</v>
       </c>
       <c r="B191">
-        <v>1626644</v>
+        <v>1626650</v>
       </c>
       <c r="C191">
-        <v>1433201</v>
+        <v>1434108</v>
       </c>
       <c r="D191">
-        <v>2870031</v>
+        <v>2872553</v>
       </c>
       <c r="E191">
-        <v>12926984</v>
+        <v>12932466</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -3618,13 +3618,13 @@
         <v>3697485</v>
       </c>
       <c r="C192">
-        <v>4485112</v>
+        <v>4486482</v>
       </c>
       <c r="D192">
-        <v>8245424</v>
+        <v>8252488</v>
       </c>
       <c r="E192">
-        <v>20079269</v>
+        <v>20087901</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -3635,13 +3635,13 @@
         <v>23913858</v>
       </c>
       <c r="C193">
-        <v>21334038</v>
+        <v>21356090</v>
       </c>
       <c r="D193">
-        <v>29968717</v>
+        <v>30067594</v>
       </c>
       <c r="E193">
-        <v>57551977</v>
+        <v>57681584</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -3652,13 +3652,13 @@
         <v>16135895</v>
       </c>
       <c r="C194">
-        <v>19020236</v>
+        <v>19047691</v>
       </c>
       <c r="D194">
-        <v>25387750</v>
+        <v>25554392</v>
       </c>
       <c r="E194">
-        <v>32970346</v>
+        <v>33371221</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -3666,16 +3666,16 @@
         <v>194</v>
       </c>
       <c r="B195">
-        <v>8171325</v>
+        <v>8171338</v>
       </c>
       <c r="C195">
-        <v>11267717</v>
+        <v>11281654</v>
       </c>
       <c r="D195">
-        <v>11710268</v>
+        <v>11769048</v>
       </c>
       <c r="E195">
-        <v>7891242</v>
+        <v>7925358</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -3686,13 +3686,13 @@
         <v>24996048</v>
       </c>
       <c r="C196">
-        <v>31832752</v>
+        <v>31885602</v>
       </c>
       <c r="D196">
-        <v>29866682</v>
+        <v>30035544</v>
       </c>
       <c r="E196">
-        <v>16642094</v>
+        <v>16694947</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -3703,13 +3703,13 @@
         <v>20675018</v>
       </c>
       <c r="C197">
-        <v>23501914</v>
+        <v>23518299</v>
       </c>
       <c r="D197">
-        <v>25176384</v>
+        <v>25302336</v>
       </c>
       <c r="E197">
-        <v>21228884</v>
+        <v>21298158</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -3720,13 +3720,13 @@
         <v>6569071</v>
       </c>
       <c r="C198">
-        <v>8472648</v>
+        <v>8479764</v>
       </c>
       <c r="D198">
-        <v>12228646</v>
+        <v>12320947</v>
       </c>
       <c r="E198">
-        <v>16672852</v>
+        <v>16848478</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -3737,13 +3737,13 @@
         <v>26941082</v>
       </c>
       <c r="C199">
-        <v>34609916</v>
+        <v>34628624</v>
       </c>
       <c r="D199">
-        <v>36378345</v>
+        <v>36475111</v>
       </c>
       <c r="E199">
-        <v>26177579</v>
+        <v>26282183</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -3754,13 +3754,13 @@
         <v>25240533</v>
       </c>
       <c r="C200">
-        <v>30600001</v>
+        <v>30613899</v>
       </c>
       <c r="D200">
-        <v>32064980</v>
+        <v>32116074</v>
       </c>
       <c r="E200">
-        <v>23974538</v>
+        <v>24005332</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -3771,13 +3771,13 @@
         <v>238845</v>
       </c>
       <c r="C201">
-        <v>289131</v>
+        <v>289243</v>
       </c>
       <c r="D201">
-        <v>366596</v>
+        <v>367412</v>
       </c>
       <c r="E201">
-        <v>250004</v>
+        <v>250614</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -3788,10 +3788,10 @@
         <v>49049</v>
       </c>
       <c r="C202">
-        <v>60176</v>
+        <v>60182</v>
       </c>
       <c r="D202">
-        <v>72947</v>
+        <v>72981</v>
       </c>
       <c r="E202">
         <v>84237</v>
@@ -3805,13 +3805,13 @@
         <v>21728434</v>
       </c>
       <c r="C203">
-        <v>26639345</v>
+        <v>26664812</v>
       </c>
       <c r="D203">
-        <v>37469372</v>
+        <v>37532986</v>
       </c>
       <c r="E203">
-        <v>51155127</v>
+        <v>51219203</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -3819,16 +3819,16 @@
         <v>203</v>
       </c>
       <c r="B204">
-        <v>24304001</v>
+        <v>24305680</v>
       </c>
       <c r="C204">
-        <v>28629973</v>
+        <v>28669525</v>
       </c>
       <c r="D204">
-        <v>35117265</v>
+        <v>35192354</v>
       </c>
       <c r="E204">
-        <v>37420272</v>
+        <v>37475705</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -3836,16 +3836,16 @@
         <v>204</v>
       </c>
       <c r="B205">
-        <v>4114569</v>
+        <v>4114764</v>
       </c>
       <c r="C205">
-        <v>3525307</v>
+        <v>3527553</v>
       </c>
       <c r="D205">
-        <v>5975035</v>
+        <v>5979906</v>
       </c>
       <c r="E205">
-        <v>17856761</v>
+        <v>17864297</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -3856,13 +3856,13 @@
         <v>12220963</v>
       </c>
       <c r="C206">
-        <v>16617619</v>
+        <v>16630281</v>
       </c>
       <c r="D206">
-        <v>16350596</v>
+        <v>16438647</v>
       </c>
       <c r="E206">
-        <v>7268480</v>
+        <v>7313316</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -3873,13 +3873,13 @@
         <v>13459488</v>
       </c>
       <c r="C207">
-        <v>14916294</v>
+        <v>14923159</v>
       </c>
       <c r="D207">
-        <v>14145055</v>
+        <v>14219674</v>
       </c>
       <c r="E207">
-        <v>6164980</v>
+        <v>6205904</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -3890,13 +3890,13 @@
         <v>18934534</v>
       </c>
       <c r="C208">
-        <v>23973683</v>
+        <v>23984717</v>
       </c>
       <c r="D208">
-        <v>26186257</v>
+        <v>26324397</v>
       </c>
       <c r="E208">
-        <v>16220482</v>
+        <v>16328156</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -3907,13 +3907,13 @@
         <v>3392416</v>
       </c>
       <c r="C209">
-        <v>5591242</v>
+        <v>5596693</v>
       </c>
       <c r="D209">
-        <v>5941752</v>
+        <v>5996803</v>
       </c>
       <c r="E209">
-        <v>2877437</v>
+        <v>2950549</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -3924,13 +3924,13 @@
         <v>14067827</v>
       </c>
       <c r="C210">
-        <v>19459935</v>
+        <v>19468891</v>
       </c>
       <c r="D210">
-        <v>23858590</v>
+        <v>23984451</v>
       </c>
       <c r="E210">
-        <v>17836545</v>
+        <v>17954946</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -3941,13 +3941,13 @@
         <v>6445276</v>
       </c>
       <c r="C211">
-        <v>10788876</v>
+        <v>10792344</v>
       </c>
       <c r="D211">
-        <v>15311031</v>
+        <v>15331980</v>
       </c>
       <c r="E211">
-        <v>12025716</v>
+        <v>12055190</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -3958,13 +3958,13 @@
         <v>4008972</v>
       </c>
       <c r="C212">
-        <v>5761627</v>
+        <v>5763335</v>
       </c>
       <c r="D212">
-        <v>9684338</v>
+        <v>9707908</v>
       </c>
       <c r="E212">
-        <v>13385671</v>
+        <v>13426421</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -3975,13 +3975,13 @@
         <v>12344201</v>
       </c>
       <c r="C213">
-        <v>16022312</v>
+        <v>16029686</v>
       </c>
       <c r="D213">
-        <v>16114620</v>
+        <v>16199629</v>
       </c>
       <c r="E213">
-        <v>7541626</v>
+        <v>7591689</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -3992,13 +3992,13 @@
         <v>10884006</v>
       </c>
       <c r="C214">
-        <v>14654125</v>
+        <v>14654147</v>
       </c>
       <c r="D214">
-        <v>15587037</v>
+        <v>15601896</v>
       </c>
       <c r="E214">
-        <v>6568391</v>
+        <v>6584316</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4009,13 +4009,13 @@
         <v>11316633</v>
       </c>
       <c r="C215">
-        <v>16276038</v>
+        <v>16276062</v>
       </c>
       <c r="D215">
-        <v>19087121</v>
+        <v>19105316</v>
       </c>
       <c r="E215">
-        <v>10286347</v>
+        <v>10311288</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4026,13 +4026,13 @@
         <v>16717872</v>
       </c>
       <c r="C216">
-        <v>21714579</v>
+        <v>21716178</v>
       </c>
       <c r="D216">
-        <v>23059540</v>
+        <v>23091181</v>
       </c>
       <c r="E216">
-        <v>9200523</v>
+        <v>9224939</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4043,13 +4043,13 @@
         <v>13409654</v>
       </c>
       <c r="C217">
-        <v>19633620</v>
+        <v>19637348</v>
       </c>
       <c r="D217">
-        <v>24710521</v>
+        <v>24739745</v>
       </c>
       <c r="E217">
-        <v>15831730</v>
+        <v>15875983</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4060,13 +4060,13 @@
         <v>15203223</v>
       </c>
       <c r="C218">
-        <v>23569558</v>
+        <v>23572202</v>
       </c>
       <c r="D218">
-        <v>30417895</v>
+        <v>30433688</v>
       </c>
       <c r="E218">
-        <v>20340316</v>
+        <v>20358983</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4077,13 +4077,13 @@
         <v>15271888</v>
       </c>
       <c r="C219">
-        <v>21353171</v>
+        <v>21356089</v>
       </c>
       <c r="D219">
-        <v>27642115</v>
+        <v>27692253</v>
       </c>
       <c r="E219">
-        <v>22719996</v>
+        <v>22783071</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4091,16 +4091,16 @@
         <v>219</v>
       </c>
       <c r="B220">
-        <v>10013068</v>
+        <v>10013174</v>
       </c>
       <c r="C220">
-        <v>14903147</v>
+        <v>14910518</v>
       </c>
       <c r="D220">
-        <v>21890423</v>
+        <v>21977912</v>
       </c>
       <c r="E220">
-        <v>22710577</v>
+        <v>22786447</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4111,13 +4111,13 @@
         <v>17072388</v>
       </c>
       <c r="C221">
-        <v>23487272</v>
+        <v>23489888</v>
       </c>
       <c r="D221">
-        <v>34680236</v>
+        <v>34704744</v>
       </c>
       <c r="E221">
-        <v>40565208</v>
+        <v>40596266</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4128,13 +4128,13 @@
         <v>5974742</v>
       </c>
       <c r="C222">
-        <v>8526816</v>
+        <v>8527981</v>
       </c>
       <c r="D222">
-        <v>11957857</v>
+        <v>11979546</v>
       </c>
       <c r="E222">
-        <v>11395168</v>
+        <v>11426803</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4145,13 +4145,13 @@
         <v>345923</v>
       </c>
       <c r="C223">
-        <v>475736</v>
+        <v>475742</v>
       </c>
       <c r="D223">
-        <v>587693</v>
+        <v>587756</v>
       </c>
       <c r="E223">
-        <v>593892</v>
+        <v>594003</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4162,10 +4162,10 @@
         <v>12614668</v>
       </c>
       <c r="C224">
-        <v>18756003</v>
+        <v>18756026</v>
       </c>
       <c r="D224">
-        <v>31842346</v>
+        <v>31843649</v>
       </c>
       <c r="E224">
         <v>40088394</v>
@@ -4179,13 +4179,13 @@
         <v>9494800</v>
       </c>
       <c r="C225">
-        <v>15074585</v>
+        <v>15074788</v>
       </c>
       <c r="D225">
-        <v>20847423</v>
+        <v>20866758</v>
       </c>
       <c r="E225">
-        <v>14909431</v>
+        <v>14935207</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4196,13 +4196,13 @@
         <v>8927316</v>
       </c>
       <c r="C226">
-        <v>12901761</v>
+        <v>12901863</v>
       </c>
       <c r="D226">
-        <v>20335473</v>
+        <v>20342513</v>
       </c>
       <c r="E226">
-        <v>20451616</v>
+        <v>20462668</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4213,13 +4213,13 @@
         <v>1319424</v>
       </c>
       <c r="C227">
-        <v>654344</v>
+        <v>654382</v>
       </c>
       <c r="D227">
-        <v>521779</v>
+        <v>523621</v>
       </c>
       <c r="E227">
-        <v>105980</v>
+        <v>107384</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4230,10 +4230,10 @@
         <v>398371</v>
       </c>
       <c r="C228">
-        <v>624560</v>
+        <v>624570</v>
       </c>
       <c r="D228">
-        <v>1062971</v>
+        <v>1063032</v>
       </c>
       <c r="E228">
         <v>1044369</v>
@@ -4244,16 +4244,16 @@
         <v>228</v>
       </c>
       <c r="B229">
-        <v>19092715</v>
+        <v>19092917</v>
       </c>
       <c r="C229">
-        <v>27682691</v>
+        <v>27696381</v>
       </c>
       <c r="D229">
-        <v>31761436</v>
+        <v>31888377</v>
       </c>
       <c r="E229">
-        <v>19518036</v>
+        <v>19583241</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4264,13 +4264,13 @@
         <v>3942164</v>
       </c>
       <c r="C230">
-        <v>5241841</v>
+        <v>5242854</v>
       </c>
       <c r="D230">
-        <v>5354927</v>
+        <v>5363900</v>
       </c>
       <c r="E230">
-        <v>2638150</v>
+        <v>2644541</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -4281,13 +4281,13 @@
         <v>4533383</v>
       </c>
       <c r="C231">
-        <v>5698843</v>
+        <v>5699815</v>
       </c>
       <c r="D231">
-        <v>10631984</v>
+        <v>10644494</v>
       </c>
       <c r="E231">
-        <v>22211223</v>
+        <v>22232158</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4298,13 +4298,13 @@
         <v>4354811</v>
       </c>
       <c r="C232">
-        <v>5153715</v>
+        <v>5153794</v>
       </c>
       <c r="D232">
-        <v>10150201</v>
+        <v>10156211</v>
       </c>
       <c r="E232">
-        <v>23676828</v>
+        <v>23698760</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4318,10 +4318,10 @@
         <v>517867</v>
       </c>
       <c r="D233">
-        <v>900645</v>
+        <v>900790</v>
       </c>
       <c r="E233">
-        <v>2046972</v>
+        <v>2047530</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4332,10 +4332,10 @@
         <v>21083418</v>
       </c>
       <c r="C234">
-        <v>25733863</v>
+        <v>25733868</v>
       </c>
       <c r="D234">
-        <v>40065707</v>
+        <v>40067196</v>
       </c>
       <c r="E234">
         <v>66412442</v>
@@ -4352,7 +4352,7 @@
         <v>1410075</v>
       </c>
       <c r="D235">
-        <v>2315531</v>
+        <v>2315617</v>
       </c>
       <c r="E235">
         <v>4062684</v>
@@ -4369,10 +4369,10 @@
         <v>2170394</v>
       </c>
       <c r="D236">
-        <v>3247178</v>
+        <v>3247298</v>
       </c>
       <c r="E236">
-        <v>4437845</v>
+        <v>4438513</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -4383,13 +4383,13 @@
         <v>10584366</v>
       </c>
       <c r="C237">
-        <v>19045879</v>
+        <v>19046282</v>
       </c>
       <c r="D237">
-        <v>28019395</v>
+        <v>28031316</v>
       </c>
       <c r="E237">
-        <v>20316411</v>
+        <v>20327084</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -4400,13 +4400,13 @@
         <v>16685128</v>
       </c>
       <c r="C238">
-        <v>25231908</v>
+        <v>25232819</v>
       </c>
       <c r="D238">
-        <v>36794047</v>
+        <v>36835065</v>
       </c>
       <c r="E238">
-        <v>32154372</v>
+        <v>32208301</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4420,10 +4420,10 @@
         <v>435788</v>
       </c>
       <c r="D239">
-        <v>656367</v>
+        <v>656395</v>
       </c>
       <c r="E239">
-        <v>526148</v>
+        <v>526227</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -4434,10 +4434,10 @@
         <v>15082810</v>
       </c>
       <c r="C240">
-        <v>17961678</v>
+        <v>17961864</v>
       </c>
       <c r="D240">
-        <v>36292486</v>
+        <v>36295232</v>
       </c>
       <c r="E240">
         <v>81675488</v>
@@ -4451,13 +4451,13 @@
         <v>195998</v>
       </c>
       <c r="C241">
-        <v>243626</v>
+        <v>243627</v>
       </c>
       <c r="D241">
-        <v>526271</v>
+        <v>526311</v>
       </c>
       <c r="E241">
-        <v>1108081</v>
+        <v>1108348</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -4468,13 +4468,13 @@
         <v>5581985</v>
       </c>
       <c r="C242">
-        <v>5446955</v>
+        <v>5447562</v>
       </c>
       <c r="D242">
-        <v>10166006</v>
+        <v>10173190</v>
       </c>
       <c r="E242">
-        <v>27224451</v>
+        <v>27245295</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -4485,13 +4485,13 @@
         <v>11590456</v>
       </c>
       <c r="C243">
-        <v>15557648</v>
+        <v>15561481</v>
       </c>
       <c r="D243">
-        <v>27841913</v>
+        <v>27869560</v>
       </c>
       <c r="E243">
-        <v>53452223</v>
+        <v>53492931</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4502,13 +4502,13 @@
         <v>13481637</v>
       </c>
       <c r="C244">
-        <v>13857055</v>
+        <v>13858598</v>
       </c>
       <c r="D244">
-        <v>25608041</v>
+        <v>25626137</v>
       </c>
       <c r="E244">
-        <v>64066658</v>
+        <v>64115709</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -4519,10 +4519,10 @@
         <v>14497934</v>
       </c>
       <c r="C245">
-        <v>17228743</v>
+        <v>17230088</v>
       </c>
       <c r="D245">
-        <v>29505667</v>
+        <v>29510590</v>
       </c>
       <c r="E245">
         <v>64946374</v>
@@ -4536,10 +4536,10 @@
         <v>160608</v>
       </c>
       <c r="C246">
-        <v>218627</v>
+        <v>218645</v>
       </c>
       <c r="D246">
-        <v>369515</v>
+        <v>369581</v>
       </c>
       <c r="E246">
         <v>771568</v>
@@ -4553,10 +4553,10 @@
         <v>40152</v>
       </c>
       <c r="C247">
-        <v>54657</v>
+        <v>54661</v>
       </c>
       <c r="D247">
-        <v>73903</v>
+        <v>73916</v>
       </c>
       <c r="E247">
         <v>171460</v>
@@ -4570,10 +4570,10 @@
         <v>1583076</v>
       </c>
       <c r="C248">
-        <v>2277013</v>
+        <v>2277062</v>
       </c>
       <c r="D248">
-        <v>2799037</v>
+        <v>2799352</v>
       </c>
       <c r="E248">
         <v>2269799</v>
@@ -4587,13 +4587,13 @@
         <v>22890</v>
       </c>
       <c r="C249">
-        <v>32469</v>
+        <v>32470</v>
       </c>
       <c r="D249">
-        <v>57971</v>
+        <v>57974</v>
       </c>
       <c r="E249">
-        <v>75595</v>
+        <v>75609</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -4604,13 +4604,13 @@
         <v>26799036</v>
       </c>
       <c r="C250">
-        <v>30379309</v>
+        <v>30384157</v>
       </c>
       <c r="D250">
-        <v>44753628</v>
+        <v>44792433</v>
       </c>
       <c r="E250">
-        <v>71480402</v>
+        <v>71515704</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -4621,13 +4621,13 @@
         <v>37518969</v>
       </c>
       <c r="C251">
-        <v>45469055</v>
+        <v>45499209</v>
       </c>
       <c r="D251">
-        <v>64386704</v>
+        <v>64458772</v>
       </c>
       <c r="E251">
-        <v>91115337</v>
+        <v>91160426</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -4638,13 +4638,13 @@
         <v>31523213</v>
       </c>
       <c r="C252">
-        <v>37600277</v>
+        <v>37600290</v>
       </c>
       <c r="D252">
-        <v>58369540</v>
+        <v>58392152</v>
       </c>
       <c r="E252">
-        <v>97372676</v>
+        <v>97418233</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -4655,13 +4655,13 @@
         <v>4125659</v>
       </c>
       <c r="C253">
-        <v>5579592</v>
+        <v>5579979</v>
       </c>
       <c r="D253">
-        <v>8353426</v>
+        <v>8354536</v>
       </c>
       <c r="E253">
-        <v>12061118</v>
+        <v>12062181</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -4672,13 +4672,13 @@
         <v>6320068</v>
       </c>
       <c r="C254">
-        <v>7640555</v>
+        <v>7642038</v>
       </c>
       <c r="D254">
-        <v>12711755</v>
+        <v>12713218</v>
       </c>
       <c r="E254">
-        <v>26933557</v>
+        <v>26935422</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -4689,13 +4689,13 @@
         <v>287837</v>
       </c>
       <c r="C255">
-        <v>363886</v>
+        <v>363912</v>
       </c>
       <c r="D255">
-        <v>546486</v>
+        <v>546558</v>
       </c>
       <c r="E255">
-        <v>792336</v>
+        <v>792406</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -4706,13 +4706,13 @@
         <v>10982448</v>
       </c>
       <c r="C256">
-        <v>13922442</v>
+        <v>13922443</v>
       </c>
       <c r="D256">
-        <v>19598967</v>
+        <v>19599588</v>
       </c>
       <c r="E256">
-        <v>26096551</v>
+        <v>26099085</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -4723,13 +4723,13 @@
         <v>2102581</v>
       </c>
       <c r="C257">
-        <v>2622087</v>
+        <v>2622092</v>
       </c>
       <c r="D257">
-        <v>3422626</v>
+        <v>3423101</v>
       </c>
       <c r="E257">
-        <v>3900686</v>
+        <v>3901228</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -4743,10 +4743,10 @@
         <v>4785217</v>
       </c>
       <c r="D258">
-        <v>7299034</v>
+        <v>7299267</v>
       </c>
       <c r="E258">
-        <v>10833683</v>
+        <v>10834796</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -4760,10 +4760,10 @@
         <v>865412</v>
       </c>
       <c r="D259">
-        <v>1193111</v>
+        <v>1193149</v>
       </c>
       <c r="E259">
-        <v>1887687</v>
+        <v>1887881</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -4771,16 +4771,16 @@
         <v>259</v>
       </c>
       <c r="B260">
-        <v>10511972</v>
+        <v>10512023</v>
       </c>
       <c r="C260">
-        <v>15456287</v>
+        <v>15456531</v>
       </c>
       <c r="D260">
-        <v>27014289</v>
+        <v>27042277</v>
       </c>
       <c r="E260">
-        <v>32565535</v>
+        <v>32598122</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -4794,10 +4794,10 @@
         <v>442018</v>
       </c>
       <c r="D261">
-        <v>1179239</v>
+        <v>1179293</v>
       </c>
       <c r="E261">
-        <v>2684183</v>
+        <v>2684765</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -4808,13 +4808,13 @@
         <v>8745502</v>
       </c>
       <c r="C262">
-        <v>15244647</v>
+        <v>15244969</v>
       </c>
       <c r="D262">
-        <v>28481896</v>
+        <v>28509537</v>
       </c>
       <c r="E262">
-        <v>33462162</v>
+        <v>33495290</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -4825,10 +4825,10 @@
         <v>653791</v>
       </c>
       <c r="C263">
-        <v>841181</v>
+        <v>841186</v>
       </c>
       <c r="D263">
-        <v>1395726</v>
+        <v>1395940</v>
       </c>
       <c r="E263">
         <v>2258136</v>
@@ -4839,16 +4839,16 @@
         <v>263</v>
       </c>
       <c r="B264">
-        <v>1359669</v>
+        <v>1359677</v>
       </c>
       <c r="C264">
-        <v>1447883</v>
+        <v>1447889</v>
       </c>
       <c r="D264">
-        <v>2848971</v>
+        <v>2849113</v>
       </c>
       <c r="E264">
-        <v>6477100</v>
+        <v>6478787</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -4856,16 +4856,16 @@
         <v>264</v>
       </c>
       <c r="B265">
-        <v>716582</v>
+        <v>716586</v>
       </c>
       <c r="C265">
-        <v>827362</v>
+        <v>827365</v>
       </c>
       <c r="D265">
-        <v>1558871</v>
+        <v>1558949</v>
       </c>
       <c r="E265">
-        <v>2956937</v>
+        <v>2957707</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -4876,13 +4876,13 @@
         <v>3918119</v>
       </c>
       <c r="C266">
-        <v>5294907</v>
+        <v>5295146</v>
       </c>
       <c r="D266">
-        <v>10319553</v>
+        <v>10321762</v>
       </c>
       <c r="E266">
-        <v>22188351</v>
+        <v>22194660</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -4890,16 +4890,16 @@
         <v>266</v>
       </c>
       <c r="B267">
-        <v>881947</v>
+        <v>881953</v>
       </c>
       <c r="C267">
-        <v>1447883</v>
+        <v>1447889</v>
       </c>
       <c r="D267">
-        <v>3225250</v>
+        <v>3225411</v>
       </c>
       <c r="E267">
-        <v>6125083</v>
+        <v>6126679</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -4913,10 +4913,10 @@
         <v>2698635</v>
       </c>
       <c r="D268">
-        <v>5896197</v>
+        <v>5896463</v>
       </c>
       <c r="E268">
-        <v>8186758</v>
+        <v>8188534</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -4930,10 +4930,10 @@
         <v>5187894</v>
       </c>
       <c r="D269">
-        <v>12185475</v>
+        <v>12186023</v>
       </c>
       <c r="E269">
-        <v>19527431</v>
+        <v>19531667</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -4944,13 +4944,13 @@
         <v>5549318</v>
       </c>
       <c r="C270">
-        <v>11278607</v>
+        <v>11278804</v>
       </c>
       <c r="D270">
-        <v>22238432</v>
+        <v>22241133</v>
       </c>
       <c r="E270">
-        <v>28375074</v>
+        <v>28382614</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -4961,13 +4961,13 @@
         <v>500677</v>
       </c>
       <c r="C271">
-        <v>846608</v>
+        <v>846613</v>
       </c>
       <c r="D271">
-        <v>1963527</v>
+        <v>1963625</v>
       </c>
       <c r="E271">
-        <v>3181721</v>
+        <v>3182222</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -4978,13 +4978,13 @@
         <v>827650</v>
       </c>
       <c r="C272">
-        <v>1652900</v>
+        <v>1652912</v>
       </c>
       <c r="D272">
-        <v>4201035</v>
+        <v>4201243</v>
       </c>
       <c r="E272">
-        <v>7190689</v>
+        <v>7191821</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -4995,13 +4995,13 @@
         <v>2870386</v>
       </c>
       <c r="C273">
-        <v>6083272</v>
+        <v>6083468</v>
       </c>
       <c r="D273">
-        <v>11204766</v>
+        <v>11207019</v>
       </c>
       <c r="E273">
-        <v>12835318</v>
+        <v>12839212</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5012,13 +5012,13 @@
         <v>1255794</v>
       </c>
       <c r="C274">
-        <v>2542743</v>
+        <v>2542825</v>
       </c>
       <c r="D274">
-        <v>5602383</v>
+        <v>5603510</v>
       </c>
       <c r="E274">
-        <v>9515839</v>
+        <v>9518726</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -5029,13 +5029,13 @@
         <v>17970009</v>
       </c>
       <c r="C275">
-        <v>27574052</v>
+        <v>27574105</v>
       </c>
       <c r="D275">
-        <v>57505668</v>
+        <v>57532462</v>
       </c>
       <c r="E275">
-        <v>71089671</v>
+        <v>71112008</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -5049,10 +5049,10 @@
         <v>780344</v>
       </c>
       <c r="D276">
-        <v>1991371</v>
+        <v>1991421</v>
       </c>
       <c r="E276">
-        <v>4417174</v>
+        <v>4417531</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -5063,13 +5063,13 @@
         <v>2059354</v>
       </c>
       <c r="C277">
-        <v>2421552</v>
+        <v>2421555</v>
       </c>
       <c r="D277">
-        <v>4692400</v>
+        <v>4692630</v>
       </c>
       <c r="E277">
-        <v>7936147</v>
+        <v>7936515</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -5080,13 +5080,13 @@
         <v>5202641</v>
       </c>
       <c r="C278">
-        <v>7916244</v>
+        <v>7916467</v>
       </c>
       <c r="D278">
-        <v>13119794</v>
+        <v>13120230</v>
       </c>
       <c r="E278">
-        <v>15187079</v>
+        <v>15187861</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5100,10 +5100,10 @@
         <v>1628299</v>
       </c>
       <c r="D279">
-        <v>3523356</v>
+        <v>3523448</v>
       </c>
       <c r="E279">
-        <v>6458743</v>
+        <v>6459271</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -5117,10 +5117,10 @@
         <v>1628299</v>
       </c>
       <c r="D280">
-        <v>2926177</v>
+        <v>2926254</v>
       </c>
       <c r="E280">
-        <v>4613388</v>
+        <v>4613765</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5131,13 +5131,13 @@
         <v>4024828</v>
       </c>
       <c r="C281">
-        <v>7880485</v>
+        <v>7880543</v>
       </c>
       <c r="D281">
-        <v>17819496</v>
+        <v>17820235</v>
       </c>
       <c r="E281">
-        <v>20861629</v>
+        <v>20863963</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -5148,13 +5148,13 @@
         <v>139379</v>
       </c>
       <c r="C282">
-        <v>303550</v>
+        <v>303557</v>
       </c>
       <c r="D282">
-        <v>831939</v>
+        <v>831963</v>
       </c>
       <c r="E282">
-        <v>1215818</v>
+        <v>1215930</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -5165,13 +5165,13 @@
         <v>598511</v>
       </c>
       <c r="C283">
-        <v>1127472</v>
+        <v>1127499</v>
       </c>
       <c r="D283">
-        <v>3146898</v>
+        <v>3146989</v>
       </c>
       <c r="E283">
-        <v>5526443</v>
+        <v>5526955</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -5182,13 +5182,13 @@
         <v>819877</v>
       </c>
       <c r="C284">
-        <v>1532206</v>
+        <v>1532242</v>
       </c>
       <c r="D284">
-        <v>3797981</v>
+        <v>3798091</v>
       </c>
       <c r="E284">
-        <v>5360650</v>
+        <v>5361146</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -5202,10 +5202,10 @@
         <v>1560688</v>
       </c>
       <c r="D285">
-        <v>3837914</v>
+        <v>3838011</v>
       </c>
       <c r="E285">
-        <v>6515331</v>
+        <v>6515859</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -5219,10 +5219,10 @@
         <v>415736</v>
       </c>
       <c r="D286">
-        <v>656897</v>
+        <v>656914</v>
       </c>
       <c r="E286">
-        <v>768898</v>
+        <v>768961</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -5233,10 +5233,10 @@
         <v>22703486</v>
       </c>
       <c r="C287">
-        <v>28684389</v>
+        <v>28685067</v>
       </c>
       <c r="D287">
-        <v>42881168</v>
+        <v>42890064</v>
       </c>
       <c r="E287">
         <v>62806230</v>
@@ -5250,10 +5250,10 @@
         <v>15858721</v>
       </c>
       <c r="C288">
-        <v>20302093</v>
+        <v>20303668</v>
       </c>
       <c r="D288">
-        <v>36263634</v>
+        <v>36273194</v>
       </c>
       <c r="E288">
         <v>74515498</v>
@@ -5267,13 +5267,13 @@
         <v>262387</v>
       </c>
       <c r="C289">
-        <v>273776</v>
+        <v>273855</v>
       </c>
       <c r="D289">
-        <v>439690</v>
+        <v>439773</v>
       </c>
       <c r="E289">
-        <v>853315</v>
+        <v>853406</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -5284,13 +5284,13 @@
         <v>5613911</v>
       </c>
       <c r="C290">
-        <v>5244549</v>
+        <v>5244649</v>
       </c>
       <c r="D290">
-        <v>9206145</v>
+        <v>9208016</v>
       </c>
       <c r="E290">
-        <v>25650560</v>
+        <v>25653711</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -5301,10 +5301,10 @@
         <v>6331734</v>
       </c>
       <c r="C291">
-        <v>9527077</v>
+        <v>9528332</v>
       </c>
       <c r="D291">
-        <v>18675000</v>
+        <v>18680207</v>
       </c>
       <c r="E291">
         <v>39687979</v>
@@ -5318,10 +5318,10 @@
         <v>5076983</v>
       </c>
       <c r="C292">
-        <v>6249220</v>
+        <v>6249272</v>
       </c>
       <c r="D292">
-        <v>8982634</v>
+        <v>8984526</v>
       </c>
       <c r="E292">
         <v>12390979</v>
@@ -5335,10 +5335,10 @@
         <v>14766264</v>
       </c>
       <c r="C293">
-        <v>24184866</v>
+        <v>24185077</v>
       </c>
       <c r="D293">
-        <v>35575012</v>
+        <v>35581440</v>
       </c>
       <c r="E293">
         <v>38770843</v>
@@ -5352,13 +5352,13 @@
         <v>1161046</v>
       </c>
       <c r="C294">
-        <v>1308950</v>
+        <v>1308958</v>
       </c>
       <c r="D294">
-        <v>1783458</v>
+        <v>1783813</v>
       </c>
       <c r="E294">
-        <v>2425292</v>
+        <v>2425830</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -5369,13 +5369,13 @@
         <v>12064917</v>
       </c>
       <c r="C295">
-        <v>18114868</v>
+        <v>18118390</v>
       </c>
       <c r="D295">
-        <v>27025908</v>
+        <v>27050627</v>
       </c>
       <c r="E295">
-        <v>27124956</v>
+        <v>27172128</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -5386,13 +5386,13 @@
         <v>12409005</v>
       </c>
       <c r="C296">
-        <v>17524630</v>
+        <v>17526030</v>
       </c>
       <c r="D296">
-        <v>25500174</v>
+        <v>25522341</v>
       </c>
       <c r="E296">
-        <v>26975140</v>
+        <v>27019228</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -5403,13 +5403,13 @@
         <v>7773169</v>
       </c>
       <c r="C297">
-        <v>9717053</v>
+        <v>9717812</v>
       </c>
       <c r="D297">
-        <v>14074072</v>
+        <v>14083939</v>
       </c>
       <c r="E297">
-        <v>16985054</v>
+        <v>16996293</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -5420,13 +5420,13 @@
         <v>9425588</v>
       </c>
       <c r="C298">
-        <v>12925359</v>
+        <v>12927106</v>
       </c>
       <c r="D298">
-        <v>21128802</v>
+        <v>21146558</v>
       </c>
       <c r="E298">
-        <v>27664819</v>
+        <v>27711728</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -5437,13 +5437,13 @@
         <v>10117506</v>
       </c>
       <c r="C299">
-        <v>13135885</v>
+        <v>13136887</v>
       </c>
       <c r="D299">
-        <v>22832492</v>
+        <v>22842103</v>
       </c>
       <c r="E299">
-        <v>36575022</v>
+        <v>36598781</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -5454,13 +5454,13 @@
         <v>7827144</v>
       </c>
       <c r="C300">
-        <v>11795000</v>
+        <v>11797294</v>
       </c>
       <c r="D300">
-        <v>16538242</v>
+        <v>16553369</v>
       </c>
       <c r="E300">
-        <v>14550037</v>
+        <v>14575341</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -5471,13 +5471,13 @@
         <v>12057753</v>
       </c>
       <c r="C301">
-        <v>16755066</v>
+        <v>16755886</v>
       </c>
       <c r="D301">
-        <v>22469405</v>
+        <v>22477838</v>
       </c>
       <c r="E301">
-        <v>20886274</v>
+        <v>20897858</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -5488,10 +5488,10 @@
         <v>351901</v>
       </c>
       <c r="C302">
-        <v>510801</v>
+        <v>510805</v>
       </c>
       <c r="D302">
-        <v>715163</v>
+        <v>715206</v>
       </c>
       <c r="E302">
         <v>803656</v>
@@ -5505,13 +5505,13 @@
         <v>1490789</v>
       </c>
       <c r="C303">
-        <v>1980925</v>
+        <v>1980937</v>
       </c>
       <c r="D303">
-        <v>3083536</v>
+        <v>3083719</v>
       </c>
       <c r="E303">
-        <v>4144013</v>
+        <v>4144589</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -5522,13 +5522,13 @@
         <v>916129</v>
       </c>
       <c r="C304">
-        <v>1736355</v>
+        <v>1736394</v>
       </c>
       <c r="D304">
-        <v>2125360</v>
+        <v>2126446</v>
       </c>
       <c r="E304">
-        <v>1050020</v>
+        <v>1050741</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -5539,13 +5539,13 @@
         <v>5748709</v>
       </c>
       <c r="C305">
-        <v>8976626</v>
+        <v>8976830</v>
       </c>
       <c r="D305">
-        <v>14114571</v>
+        <v>14121782</v>
       </c>
       <c r="E305">
-        <v>14910280</v>
+        <v>14920520</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -5556,13 +5556,13 @@
         <v>8082269</v>
       </c>
       <c r="C306">
-        <v>11806720</v>
+        <v>11807692</v>
       </c>
       <c r="D306">
-        <v>18206760</v>
+        <v>18209841</v>
       </c>
       <c r="E306">
-        <v>19308240</v>
+        <v>19316478</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -5573,13 +5573,13 @@
         <v>5176129</v>
       </c>
       <c r="C307">
-        <v>8190352</v>
+        <v>8190538</v>
       </c>
       <c r="D307">
-        <v>14005578</v>
+        <v>14012734</v>
       </c>
       <c r="E307">
-        <v>17220324</v>
+        <v>17232149</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -5590,10 +5590,10 @@
         <v>128391</v>
       </c>
       <c r="C308">
-        <v>220974</v>
+        <v>220975</v>
       </c>
       <c r="D308">
-        <v>352502</v>
+        <v>352507</v>
       </c>
       <c r="E308">
         <v>374671</v>
@@ -5607,13 +5607,13 @@
         <v>3901785</v>
       </c>
       <c r="C309">
-        <v>5136080</v>
+        <v>5136503</v>
       </c>
       <c r="D309">
-        <v>9206243</v>
+        <v>9207801</v>
       </c>
       <c r="E309">
-        <v>14698314</v>
+        <v>14704585</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -5624,10 +5624,10 @@
         <v>5920518</v>
       </c>
       <c r="C310">
-        <v>9273496</v>
+        <v>9273529</v>
       </c>
       <c r="D310">
-        <v>16593815</v>
+        <v>16595324</v>
       </c>
       <c r="E310">
         <v>25333943</v>
@@ -5644,10 +5644,10 @@
         <v>1609931</v>
       </c>
       <c r="D311">
-        <v>3786441</v>
+        <v>3786459</v>
       </c>
       <c r="E311">
-        <v>5967175</v>
+        <v>5967756</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -5661,10 +5661,10 @@
         <v>294825</v>
       </c>
       <c r="D312">
-        <v>701916</v>
+        <v>701953</v>
       </c>
       <c r="E312">
-        <v>1742988</v>
+        <v>1745554</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -5678,10 +5678,10 @@
         <v>530099</v>
       </c>
       <c r="D313">
-        <v>1320852</v>
+        <v>1320858</v>
       </c>
       <c r="E313">
-        <v>2198433</v>
+        <v>2198647</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -5695,10 +5695,10 @@
         <v>765699</v>
       </c>
       <c r="D314">
-        <v>1585022</v>
+        <v>1585029</v>
       </c>
       <c r="E314">
-        <v>1695934</v>
+        <v>1696099</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -5709,13 +5709,13 @@
         <v>28707008</v>
       </c>
       <c r="C315">
-        <v>33584794</v>
+        <v>33602811</v>
       </c>
       <c r="D315">
-        <v>50038244</v>
+        <v>50088098</v>
       </c>
       <c r="E315">
-        <v>76857442</v>
+        <v>76896259</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -5723,16 +5723,16 @@
         <v>315</v>
       </c>
       <c r="B316">
-        <v>14594521</v>
+        <v>14595541</v>
       </c>
       <c r="C316">
-        <v>18432951</v>
+        <v>18451291</v>
       </c>
       <c r="D316">
-        <v>23540390</v>
+        <v>23575735</v>
       </c>
       <c r="E316">
-        <v>25541108</v>
+        <v>25571878</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -5743,13 +5743,13 @@
         <v>28850634</v>
       </c>
       <c r="C317">
-        <v>33319480</v>
+        <v>33343522</v>
       </c>
       <c r="D317">
-        <v>46647885</v>
+        <v>46744483</v>
       </c>
       <c r="E317">
-        <v>65738361</v>
+        <v>65827869</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -5760,13 +5760,13 @@
         <v>22712420</v>
       </c>
       <c r="C318">
-        <v>30250268</v>
+        <v>30268479</v>
       </c>
       <c r="D318">
-        <v>35843454</v>
+        <v>35914894</v>
       </c>
       <c r="E318">
-        <v>30877438</v>
+        <v>30920651</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -5777,13 +5777,13 @@
         <v>19101661</v>
       </c>
       <c r="C319">
-        <v>23778141</v>
+        <v>23788471</v>
       </c>
       <c r="D319">
-        <v>29553722</v>
+        <v>29624672</v>
       </c>
       <c r="E319">
-        <v>29176428</v>
+        <v>29224790</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -5794,13 +5794,13 @@
         <v>13625338</v>
       </c>
       <c r="C320">
-        <v>16003999</v>
+        <v>16021767</v>
       </c>
       <c r="D320">
-        <v>23268289</v>
+        <v>23332443</v>
       </c>
       <c r="E320">
-        <v>33962466</v>
+        <v>34019053</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -5811,13 +5811,13 @@
         <v>22422286</v>
       </c>
       <c r="C321">
-        <v>31237983</v>
+        <v>31267424</v>
       </c>
       <c r="D321">
-        <v>42391918</v>
+        <v>42489334</v>
       </c>
       <c r="E321">
-        <v>45868224</v>
+        <v>45933059</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -5828,13 +5828,13 @@
         <v>1533055</v>
       </c>
       <c r="C322">
-        <v>1849957</v>
+        <v>1850058</v>
       </c>
       <c r="D322">
-        <v>2678043</v>
+        <v>2678426</v>
       </c>
       <c r="E322">
-        <v>3936987</v>
+        <v>3937438</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -5845,13 +5845,13 @@
         <v>19582446</v>
       </c>
       <c r="C323">
-        <v>25648151</v>
+        <v>25653586</v>
       </c>
       <c r="D323">
-        <v>38666095</v>
+        <v>38742417</v>
       </c>
       <c r="E323">
-        <v>55288416</v>
+        <v>55368468</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -5862,13 +5862,13 @@
         <v>11054607</v>
       </c>
       <c r="C324">
-        <v>13157788</v>
+        <v>13160576</v>
       </c>
       <c r="D324">
-        <v>21769455</v>
+        <v>21812424</v>
       </c>
       <c r="E324">
-        <v>41976841</v>
+        <v>42037620</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -5879,13 +5879,13 @@
         <v>18634909</v>
       </c>
       <c r="C325">
-        <v>21405242</v>
+        <v>21409777</v>
       </c>
       <c r="D325">
-        <v>34869097</v>
+        <v>34937924</v>
       </c>
       <c r="E325">
-        <v>67238579</v>
+        <v>67335935</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -5896,13 +5896,13 @@
         <v>14604471</v>
       </c>
       <c r="C326">
-        <v>15238263</v>
+        <v>15244685</v>
       </c>
       <c r="D326">
-        <v>23045718</v>
+        <v>23091119</v>
       </c>
       <c r="E326">
-        <v>42433315</v>
+        <v>42493368</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -5913,10 +5913,10 @@
         <v>14113261</v>
       </c>
       <c r="C327">
-        <v>17026155</v>
+        <v>17027684</v>
       </c>
       <c r="D327">
-        <v>27804428</v>
+        <v>27810444</v>
       </c>
       <c r="E327">
         <v>52508459</v>
@@ -5930,13 +5930,13 @@
         <v>754277</v>
       </c>
       <c r="C328">
-        <v>920469</v>
+        <v>920536</v>
       </c>
       <c r="D328">
-        <v>1309447</v>
+        <v>1309711</v>
       </c>
       <c r="E328">
-        <v>1681333</v>
+        <v>1681525</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -5947,13 +5947,13 @@
         <v>1945650</v>
       </c>
       <c r="C329">
-        <v>2995081</v>
+        <v>2995173</v>
       </c>
       <c r="D329">
-        <v>3986595</v>
+        <v>3987382</v>
       </c>
       <c r="E329">
-        <v>3738460</v>
+        <v>3738976</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -5964,13 +5964,13 @@
         <v>1340936</v>
       </c>
       <c r="C330">
-        <v>1570212</v>
+        <v>1570326</v>
       </c>
       <c r="D330">
-        <v>2546147</v>
+        <v>2546661</v>
       </c>
       <c r="E330">
-        <v>4707733</v>
+        <v>4708271</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -5981,13 +5981,13 @@
         <v>3262651</v>
       </c>
       <c r="C331">
-        <v>3571270</v>
+        <v>3572114</v>
       </c>
       <c r="D331">
-        <v>7197721</v>
+        <v>7207267</v>
       </c>
       <c r="E331">
-        <v>23197145</v>
+        <v>23211269</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -5998,10 +5998,10 @@
         <v>33592373</v>
       </c>
       <c r="C332">
-        <v>36650427</v>
+        <v>36653210</v>
       </c>
       <c r="D332">
-        <v>58068515</v>
+        <v>58078127</v>
       </c>
       <c r="E332">
         <v>113353176</v>
@@ -6012,16 +6012,16 @@
         <v>332</v>
       </c>
       <c r="B333">
-        <v>16968619</v>
+        <v>16968620</v>
       </c>
       <c r="C333">
-        <v>19602480</v>
+        <v>19607786</v>
       </c>
       <c r="D333">
-        <v>31749892</v>
+        <v>31776741</v>
       </c>
       <c r="E333">
-        <v>57311738</v>
+        <v>57343366</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -6032,10 +6032,10 @@
         <v>17268802</v>
       </c>
       <c r="C334">
-        <v>17697706</v>
+        <v>17700531</v>
       </c>
       <c r="D334">
-        <v>25562709</v>
+        <v>25565889</v>
       </c>
       <c r="E334">
         <v>45365953</v>
@@ -6049,10 +6049,10 @@
         <v>20382380</v>
       </c>
       <c r="C335">
-        <v>23434879</v>
+        <v>23437365</v>
       </c>
       <c r="D335">
-        <v>37155424</v>
+        <v>37160710</v>
       </c>
       <c r="E335">
         <v>70008566</v>
@@ -6066,13 +6066,13 @@
         <v>2002957</v>
       </c>
       <c r="C336">
-        <v>2280544</v>
+        <v>2280558</v>
       </c>
       <c r="D336">
-        <v>4279434</v>
+        <v>4280201</v>
       </c>
       <c r="E336">
-        <v>11928100</v>
+        <v>11929401</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -6083,13 +6083,13 @@
         <v>7965538</v>
       </c>
       <c r="C337">
-        <v>10662696</v>
+        <v>10663072</v>
       </c>
       <c r="D337">
-        <v>18123472</v>
+        <v>18130639</v>
       </c>
       <c r="E337">
-        <v>20038279</v>
+        <v>20042711</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -6103,10 +6103,10 @@
         <v>10825976</v>
       </c>
       <c r="D338">
-        <v>15899789</v>
+        <v>15901877</v>
       </c>
       <c r="E338">
-        <v>11231643</v>
+        <v>11233427</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -6117,13 +6117,13 @@
         <v>11688844</v>
       </c>
       <c r="C339">
-        <v>17339821</v>
+        <v>17340432</v>
       </c>
       <c r="D339">
-        <v>32090183</v>
+        <v>32102875</v>
       </c>
       <c r="E339">
-        <v>38072729</v>
+        <v>38081151</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -6137,10 +6137,10 @@
         <v>319492</v>
       </c>
       <c r="D340">
-        <v>678271</v>
+        <v>678281</v>
       </c>
       <c r="E340">
-        <v>1088491</v>
+        <v>1088528</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -6154,7 +6154,7 @@
         <v>2330336</v>
       </c>
       <c r="D341">
-        <v>5826149</v>
+        <v>5826255</v>
       </c>
       <c r="E341">
         <v>14820515</v>
@@ -6168,13 +6168,13 @@
         <v>1385441</v>
       </c>
       <c r="C342">
-        <v>1809530</v>
+        <v>1809554</v>
       </c>
       <c r="D342">
-        <v>4032647</v>
+        <v>4032803</v>
       </c>
       <c r="E342">
-        <v>8166083</v>
+        <v>8166384</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -6185,13 +6185,13 @@
         <v>787514</v>
       </c>
       <c r="C343">
-        <v>935964</v>
+        <v>935976</v>
       </c>
       <c r="D343">
-        <v>1914489</v>
+        <v>1914563</v>
       </c>
       <c r="E343">
-        <v>3590760</v>
+        <v>3590892</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -6205,10 +6205,10 @@
         <v>496988</v>
       </c>
       <c r="D344">
-        <v>1070954</v>
+        <v>1070971</v>
       </c>
       <c r="E344">
-        <v>1762318</v>
+        <v>1762378</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -6222,10 +6222,10 @@
         <v>3067073</v>
       </c>
       <c r="D345">
-        <v>6088945</v>
+        <v>6089011</v>
       </c>
       <c r="E345">
-        <v>6612668</v>
+        <v>6612944</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -6239,10 +6239,10 @@
         <v>386838</v>
       </c>
       <c r="D346">
-        <v>1009724</v>
+        <v>1009736</v>
       </c>
       <c r="E346">
-        <v>1641766</v>
+        <v>1641834</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -6256,10 +6256,10 @@
         <v>469732</v>
       </c>
       <c r="D347">
-        <v>1070920</v>
+        <v>1070932</v>
       </c>
       <c r="E347">
-        <v>1869789</v>
+        <v>1869867</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -6270,13 +6270,13 @@
         <v>1918512</v>
       </c>
       <c r="C348">
-        <v>2989794</v>
+        <v>2989798</v>
       </c>
       <c r="D348">
-        <v>5220563</v>
+        <v>5220861</v>
       </c>
       <c r="E348">
-        <v>5445830</v>
+        <v>5446148</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -6287,13 +6287,13 @@
         <v>472015</v>
       </c>
       <c r="C349">
-        <v>585838</v>
+        <v>585839</v>
       </c>
       <c r="D349">
-        <v>1324056</v>
+        <v>1324131</v>
       </c>
       <c r="E349">
-        <v>3289066</v>
+        <v>3289258</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -6304,13 +6304,13 @@
         <v>959256</v>
       </c>
       <c r="C350">
-        <v>1353488</v>
+        <v>1353490</v>
       </c>
       <c r="D350">
-        <v>2761602</v>
+        <v>2761760</v>
       </c>
       <c r="E350">
-        <v>4367448</v>
+        <v>4367703</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -6321,13 +6321,13 @@
         <v>582592</v>
       </c>
       <c r="C351">
-        <v>1156150</v>
+        <v>1156156</v>
       </c>
       <c r="D351">
-        <v>2374010</v>
+        <v>2374057</v>
       </c>
       <c r="E351">
-        <v>2306530</v>
+        <v>2306688</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -6338,13 +6338,13 @@
         <v>433392</v>
       </c>
       <c r="C352">
-        <v>879155</v>
+        <v>879161</v>
       </c>
       <c r="D352">
-        <v>2346081</v>
+        <v>2346127</v>
       </c>
       <c r="E352">
-        <v>3995240</v>
+        <v>3995513</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -6355,10 +6355,10 @@
         <v>10944139</v>
       </c>
       <c r="C353">
-        <v>16546160</v>
+        <v>16546366</v>
       </c>
       <c r="D353">
-        <v>29977855</v>
+        <v>29979779</v>
       </c>
       <c r="E353">
         <v>36115129</v>
@@ -6372,13 +6372,13 @@
         <v>3336672</v>
       </c>
       <c r="C354">
-        <v>6012318</v>
+        <v>6012327</v>
       </c>
       <c r="D354">
-        <v>8692470</v>
+        <v>8692561</v>
       </c>
       <c r="E354">
-        <v>5189525</v>
+        <v>5189938</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -6389,13 +6389,13 @@
         <v>1303089</v>
       </c>
       <c r="C355">
-        <v>1982801</v>
+        <v>1982821</v>
       </c>
       <c r="D355">
-        <v>4477724</v>
+        <v>4478008</v>
       </c>
       <c r="E355">
-        <v>8294172</v>
+        <v>8295320</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -6406,13 +6406,13 @@
         <v>3075154</v>
       </c>
       <c r="C356">
-        <v>4213570</v>
+        <v>4213576</v>
       </c>
       <c r="D356">
-        <v>7371421</v>
+        <v>7371458</v>
       </c>
       <c r="E356">
-        <v>8849403</v>
+        <v>8849809</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -6423,13 +6423,13 @@
         <v>527600</v>
       </c>
       <c r="C357">
-        <v>751717</v>
+        <v>751718</v>
       </c>
       <c r="D357">
-        <v>1592820</v>
+        <v>1592828</v>
       </c>
       <c r="E357">
-        <v>2842536</v>
+        <v>2842666</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -6440,13 +6440,13 @@
         <v>1055200</v>
       </c>
       <c r="C358">
-        <v>1483652</v>
+        <v>1483653</v>
       </c>
       <c r="D358">
-        <v>3148597</v>
+        <v>3148613</v>
       </c>
       <c r="E358">
-        <v>5577806</v>
+        <v>5578061</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -6457,13 +6457,13 @@
         <v>860858</v>
       </c>
       <c r="C359">
-        <v>1880955</v>
+        <v>1881016</v>
       </c>
       <c r="D359">
-        <v>4052345</v>
+        <v>4052420</v>
       </c>
       <c r="E359">
-        <v>4021415</v>
+        <v>4021509</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -6474,13 +6474,13 @@
         <v>332261</v>
       </c>
       <c r="C360">
-        <v>664604</v>
+        <v>664625</v>
       </c>
       <c r="D360">
-        <v>1551962</v>
+        <v>1551991</v>
       </c>
       <c r="E360">
-        <v>1967926</v>
+        <v>1967973</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -6491,10 +6491,10 @@
         <v>29988851</v>
       </c>
       <c r="C361">
-        <v>46028584</v>
+        <v>46028755</v>
       </c>
       <c r="D361">
-        <v>80270940</v>
+        <v>80276350</v>
       </c>
       <c r="E361">
         <v>116685820</v>
@@ -6508,13 +6508,13 @@
         <v>167824</v>
       </c>
       <c r="C362">
-        <v>276246</v>
+        <v>276247</v>
       </c>
       <c r="D362">
-        <v>531611</v>
+        <v>531702</v>
       </c>
       <c r="E362">
-        <v>733998</v>
+        <v>734186</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -6528,10 +6528,10 @@
         <v>3364552</v>
       </c>
       <c r="D363">
-        <v>6666419</v>
+        <v>6666683</v>
       </c>
       <c r="E363">
-        <v>10735622</v>
+        <v>10737076</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -6545,10 +6545,10 @@
         <v>18792829</v>
       </c>
       <c r="D364">
-        <v>32226236</v>
+        <v>32226738</v>
       </c>
       <c r="E364">
-        <v>45600355</v>
+        <v>45604664</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -6562,10 +6562,10 @@
         <v>206062</v>
       </c>
       <c r="D365">
-        <v>467047</v>
+        <v>467054</v>
       </c>
       <c r="E365">
-        <v>4175257</v>
+        <v>4175651</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -6576,13 +6576,13 @@
         <v>253564</v>
       </c>
       <c r="C366">
-        <v>406300</v>
+        <v>406302</v>
       </c>
       <c r="D366">
-        <v>791018</v>
+        <v>791068</v>
       </c>
       <c r="E366">
-        <v>1241958</v>
+        <v>1242248</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -6593,13 +6593,13 @@
         <v>546138</v>
       </c>
       <c r="C367">
-        <v>880317</v>
+        <v>880321</v>
       </c>
       <c r="D367">
-        <v>1764578</v>
+        <v>1764690</v>
       </c>
       <c r="E367">
-        <v>2949649</v>
+        <v>2950340</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -6613,10 +6613,10 @@
         <v>1455076</v>
       </c>
       <c r="D368">
-        <v>3214052</v>
+        <v>3214099</v>
       </c>
       <c r="E368">
-        <v>7130438</v>
+        <v>7131247</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -6627,13 +6627,13 @@
         <v>156039</v>
       </c>
       <c r="C369">
-        <v>237008</v>
+        <v>237009</v>
       </c>
       <c r="D369">
-        <v>547628</v>
+        <v>547662</v>
       </c>
       <c r="E369">
-        <v>1164335</v>
+        <v>1164608</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -6644,13 +6644,13 @@
         <v>1759716</v>
       </c>
       <c r="C370">
-        <v>3244399</v>
+        <v>3244445</v>
       </c>
       <c r="D370">
-        <v>7225802</v>
+        <v>7226684</v>
       </c>
       <c r="E370">
-        <v>11824038</v>
+        <v>11827304</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -6661,13 +6661,13 @@
         <v>261776</v>
       </c>
       <c r="C371">
-        <v>354430</v>
+        <v>354435</v>
       </c>
       <c r="D371">
-        <v>778163</v>
+        <v>778258</v>
       </c>
       <c r="E371">
-        <v>1625805</v>
+        <v>1626254</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -6678,13 +6678,13 @@
         <v>1192535</v>
       </c>
       <c r="C372">
-        <v>2617331</v>
+        <v>2617367</v>
       </c>
       <c r="D372">
-        <v>6725554</v>
+        <v>6726375</v>
       </c>
       <c r="E372">
-        <v>12858642</v>
+        <v>12862193</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -6698,7 +6698,7 @@
         <v>28609091</v>
       </c>
       <c r="D373">
-        <v>45707796</v>
+        <v>45709374</v>
       </c>
       <c r="E373">
         <v>48983676</v>
@@ -6715,7 +6715,7 @@
         <v>15162001</v>
       </c>
       <c r="D374">
-        <v>24497804</v>
+        <v>24499113</v>
       </c>
       <c r="E374">
         <v>22555987</v>
@@ -6732,10 +6732,10 @@
         <v>921978</v>
       </c>
       <c r="D375">
-        <v>1670224</v>
+        <v>1670275</v>
       </c>
       <c r="E375">
-        <v>1672420</v>
+        <v>1672472</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -6746,13 +6746,13 @@
         <v>786776</v>
       </c>
       <c r="C376">
-        <v>950924</v>
+        <v>950962</v>
       </c>
       <c r="D376">
-        <v>2082674</v>
+        <v>2082767</v>
       </c>
       <c r="E376">
-        <v>4632798</v>
+        <v>4632917</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -6763,13 +6763,13 @@
         <v>2585122</v>
       </c>
       <c r="C377">
-        <v>3830109</v>
+        <v>3830265</v>
       </c>
       <c r="D377">
-        <v>8132345</v>
+        <v>8132711</v>
       </c>
       <c r="E377">
-        <v>13629826</v>
+        <v>13630177</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -6783,7 +6783,7 @@
         <v>28463126</v>
       </c>
       <c r="D378">
-        <v>44255922</v>
+        <v>44256811</v>
       </c>
       <c r="E378">
         <v>51766731</v>
@@ -6800,7 +6800,7 @@
         <v>389906</v>
       </c>
       <c r="D379">
-        <v>611270</v>
+        <v>611282</v>
       </c>
       <c r="E379">
         <v>686157</v>
@@ -6817,10 +6817,10 @@
         <v>119780</v>
       </c>
       <c r="D380">
-        <v>189141</v>
+        <v>189145</v>
       </c>
       <c r="E380">
-        <v>231383</v>
+        <v>231407</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -6834,10 +6834,10 @@
         <v>838460</v>
       </c>
       <c r="D381">
-        <v>1260940</v>
+        <v>1260963</v>
       </c>
       <c r="E381">
-        <v>1311172</v>
+        <v>1311305</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -6848,13 +6848,13 @@
         <v>984417</v>
       </c>
       <c r="C382">
-        <v>1599710</v>
+        <v>1599720</v>
       </c>
       <c r="D382">
-        <v>2734902</v>
+        <v>2734986</v>
       </c>
       <c r="E382">
-        <v>3102312</v>
+        <v>3103048</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -6865,13 +6865,13 @@
         <v>14450251</v>
       </c>
       <c r="C383">
-        <v>22088433</v>
+        <v>22088434</v>
       </c>
       <c r="D383">
-        <v>33582581</v>
+        <v>33584087</v>
       </c>
       <c r="E383">
-        <v>38009849</v>
+        <v>38018206</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -6885,10 +6885,10 @@
         <v>107950</v>
       </c>
       <c r="D384">
-        <v>180262</v>
+        <v>180265</v>
       </c>
       <c r="E384">
-        <v>225221</v>
+        <v>225235</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -6902,10 +6902,10 @@
         <v>3711117</v>
       </c>
       <c r="D385">
-        <v>5566609</v>
+        <v>5566884</v>
       </c>
       <c r="E385">
-        <v>9643828</v>
+        <v>9645048</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -6916,13 +6916,13 @@
         <v>2962806</v>
       </c>
       <c r="C386">
-        <v>4961286</v>
+        <v>4961291</v>
       </c>
       <c r="D386">
-        <v>8411616</v>
+        <v>8411743</v>
       </c>
       <c r="E386">
-        <v>8957450</v>
+        <v>8958508</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -6933,13 +6933,13 @@
         <v>2033298</v>
       </c>
       <c r="C387">
-        <v>3509202</v>
+        <v>3509206</v>
       </c>
       <c r="D387">
-        <v>7037169</v>
+        <v>7037275</v>
       </c>
       <c r="E387">
-        <v>10175663</v>
+        <v>10176865</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -6953,7 +6953,7 @@
         <v>13492580</v>
       </c>
       <c r="D388">
-        <v>32860479</v>
+        <v>32860504</v>
       </c>
       <c r="E388">
         <v>38899939</v>
@@ -6967,13 +6967,13 @@
         <v>318740</v>
       </c>
       <c r="C389">
-        <v>521473</v>
+        <v>521474</v>
       </c>
       <c r="D389">
-        <v>1620752</v>
+        <v>1620756</v>
       </c>
       <c r="E389">
-        <v>2805560</v>
+        <v>2805612</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -6984,13 +6984,13 @@
         <v>286216</v>
       </c>
       <c r="C390">
-        <v>490798</v>
+        <v>490799</v>
       </c>
       <c r="D390">
-        <v>1498431</v>
+        <v>1498435</v>
       </c>
       <c r="E390">
-        <v>2346468</v>
+        <v>2346512</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -7004,7 +7004,7 @@
         <v>980634</v>
       </c>
       <c r="D391">
-        <v>2993045</v>
+        <v>2993047</v>
       </c>
       <c r="E391">
         <v>6150188</v>
@@ -7021,10 +7021,10 @@
         <v>296524</v>
       </c>
       <c r="D392">
-        <v>1070308</v>
+        <v>1070310</v>
       </c>
       <c r="E392">
-        <v>2601519</v>
+        <v>2601567</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -7038,10 +7038,10 @@
         <v>1512468</v>
       </c>
       <c r="D393">
-        <v>4506224</v>
+        <v>4506249</v>
       </c>
       <c r="E393">
-        <v>7583984</v>
+        <v>7584044</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -7055,10 +7055,10 @@
         <v>400124</v>
       </c>
       <c r="D394">
-        <v>1326706</v>
+        <v>1326713</v>
       </c>
       <c r="E394">
-        <v>3048838</v>
+        <v>3048862</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -7072,10 +7072,10 @@
         <v>1709994</v>
       </c>
       <c r="D395">
-        <v>4944532</v>
+        <v>4944570</v>
       </c>
       <c r="E395">
-        <v>8431207</v>
+        <v>8431390</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -7089,10 +7089,10 @@
         <v>478798</v>
       </c>
       <c r="D396">
-        <v>1372167</v>
+        <v>1372177</v>
       </c>
       <c r="E396">
-        <v>2525477</v>
+        <v>2525532</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -7106,10 +7106,10 @@
         <v>896570</v>
       </c>
       <c r="D397">
-        <v>2572710</v>
+        <v>2572711</v>
       </c>
       <c r="E397">
-        <v>3987994</v>
+        <v>3988048</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -7126,7 +7126,7 @@
         <v>803972</v>
       </c>
       <c r="E398">
-        <v>1387128</v>
+        <v>1387147</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -7140,7 +7140,7 @@
         <v>10900141</v>
       </c>
       <c r="D399">
-        <v>35412421</v>
+        <v>35412474</v>
       </c>
       <c r="E399">
         <v>50168912</v>
@@ -7157,10 +7157,10 @@
         <v>558585</v>
       </c>
       <c r="D400">
-        <v>2133053</v>
+        <v>2133059</v>
       </c>
       <c r="E400">
-        <v>3622339</v>
+        <v>3622679</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -7174,10 +7174,10 @@
         <v>483109</v>
       </c>
       <c r="D401">
-        <v>1724113</v>
+        <v>1724115</v>
       </c>
       <c r="E401">
-        <v>3801464</v>
+        <v>3801816</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -7191,10 +7191,10 @@
         <v>348717</v>
       </c>
       <c r="D402">
-        <v>1397120</v>
+        <v>1397130</v>
       </c>
       <c r="E402">
-        <v>3572155</v>
+        <v>3572423</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -7208,10 +7208,10 @@
         <v>921666</v>
       </c>
       <c r="D403">
-        <v>3966145</v>
+        <v>3966157</v>
       </c>
       <c r="E403">
-        <v>10031092</v>
+        <v>10032033</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -7225,10 +7225,10 @@
         <v>2423666</v>
       </c>
       <c r="D404">
-        <v>7819568</v>
+        <v>7819585</v>
       </c>
       <c r="E404">
-        <v>8691819</v>
+        <v>8692366</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -7242,10 +7242,10 @@
         <v>157576</v>
       </c>
       <c r="D405">
-        <v>527162</v>
+        <v>527163</v>
       </c>
       <c r="E405">
-        <v>609952</v>
+        <v>609991</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -7259,10 +7259,10 @@
         <v>127561</v>
       </c>
       <c r="D406">
-        <v>410015</v>
+        <v>410016</v>
       </c>
       <c r="E406">
-        <v>457464</v>
+        <v>457493</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -7276,10 +7276,10 @@
         <v>1369867</v>
       </c>
       <c r="D407">
-        <v>5207733</v>
+        <v>5207740</v>
       </c>
       <c r="E407">
-        <v>7296207</v>
+        <v>7296561</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -7296,7 +7296,7 @@
         <v>26570</v>
       </c>
       <c r="E408">
-        <v>47378</v>
+        <v>47380</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -7313,7 +7313,7 @@
         <v>79710</v>
       </c>
       <c r="E409">
-        <v>94756</v>
+        <v>94761</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -7324,10 +7324,10 @@
         <v>7500997</v>
       </c>
       <c r="C410">
-        <v>16395704</v>
+        <v>16395712</v>
       </c>
       <c r="D410">
-        <v>35294535</v>
+        <v>35296965</v>
       </c>
       <c r="E410">
         <v>45819383</v>
@@ -7344,10 +7344,10 @@
         <v>250657</v>
       </c>
       <c r="D411">
-        <v>797291</v>
+        <v>797322</v>
       </c>
       <c r="E411">
-        <v>3604185</v>
+        <v>3604939</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -7361,10 +7361,10 @@
         <v>62664</v>
       </c>
       <c r="D412">
-        <v>149492</v>
+        <v>149498</v>
       </c>
       <c r="E412">
-        <v>212011</v>
+        <v>212055</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -7375,13 +7375,13 @@
         <v>225285</v>
       </c>
       <c r="C413">
-        <v>376780</v>
+        <v>376785</v>
       </c>
       <c r="D413">
-        <v>1156374</v>
+        <v>1156481</v>
       </c>
       <c r="E413">
-        <v>3565262</v>
+        <v>3566083</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -7395,10 +7395,10 @@
         <v>430195</v>
       </c>
       <c r="D414">
-        <v>948274</v>
+        <v>948344</v>
       </c>
       <c r="E414">
-        <v>1348249</v>
+        <v>1348616</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -7412,10 +7412,10 @@
         <v>5192222</v>
       </c>
       <c r="D415">
-        <v>12521260</v>
+        <v>12521493</v>
       </c>
       <c r="E415">
-        <v>19463072</v>
+        <v>19465456</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -7429,10 +7429,10 @@
         <v>268563</v>
       </c>
       <c r="D416">
-        <v>613286</v>
+        <v>613298</v>
       </c>
       <c r="E416">
-        <v>1001776</v>
+        <v>1001898</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -7443,13 +7443,13 @@
         <v>766633</v>
       </c>
       <c r="C417">
-        <v>1681519</v>
+        <v>1681520</v>
       </c>
       <c r="D417">
-        <v>4467890</v>
+        <v>4467929</v>
       </c>
       <c r="E417">
-        <v>5887936</v>
+        <v>5888960</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -7466,7 +7466,7 @@
         <v>41756</v>
       </c>
       <c r="E418">
-        <v>63311</v>
+        <v>63322</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -7480,7 +7480,7 @@
         <v>1294845</v>
       </c>
       <c r="D419">
-        <v>2736485</v>
+        <v>2736496</v>
       </c>
       <c r="E419">
         <v>3764599</v>
@@ -7497,7 +7497,7 @@
         <v>384407</v>
       </c>
       <c r="D420">
-        <v>838600</v>
+        <v>838604</v>
       </c>
       <c r="E420">
         <v>1276135</v>
@@ -7514,10 +7514,10 @@
         <v>2667772</v>
       </c>
       <c r="D421">
-        <v>5155315</v>
+        <v>5155905</v>
       </c>
       <c r="E421">
-        <v>5365451</v>
+        <v>5367091</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -7531,10 +7531,10 @@
         <v>1014735</v>
       </c>
       <c r="D422">
-        <v>2319892</v>
+        <v>2320157</v>
       </c>
       <c r="E422">
-        <v>3120721</v>
+        <v>3121675</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -7548,7 +7548,7 @@
         <v>2427834</v>
       </c>
       <c r="D423">
-        <v>4634369</v>
+        <v>4634388</v>
       </c>
       <c r="E423">
         <v>4976928</v>
@@ -7565,7 +7565,7 @@
         <v>2913400</v>
       </c>
       <c r="D424">
-        <v>5517106</v>
+        <v>5517129</v>
       </c>
       <c r="E424">
         <v>5104541</v>
@@ -7582,10 +7582,10 @@
         <v>491001</v>
       </c>
       <c r="D425">
-        <v>846945</v>
+        <v>847042</v>
       </c>
       <c r="E425">
-        <v>492745</v>
+        <v>492896</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -7599,7 +7599,7 @@
         <v>566495</v>
       </c>
       <c r="D426">
-        <v>1059284</v>
+        <v>1059289</v>
       </c>
       <c r="E426">
         <v>1658976</v>
@@ -7616,10 +7616,10 @@
         <v>629581</v>
       </c>
       <c r="D427">
-        <v>1464802</v>
+        <v>1464807</v>
       </c>
       <c r="E427">
-        <v>3108324</v>
+        <v>3108538</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -7633,10 +7633,10 @@
         <v>2161561</v>
       </c>
       <c r="D428">
-        <v>4852155</v>
+        <v>4852174</v>
       </c>
       <c r="E428">
-        <v>6605189</v>
+        <v>6605643</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -7650,7 +7650,7 @@
         <v>485567</v>
       </c>
       <c r="D429">
-        <v>1368242</v>
+        <v>1368248</v>
       </c>
       <c r="E429">
         <v>4785507</v>
@@ -7667,7 +7667,7 @@
         <v>1052061</v>
       </c>
       <c r="D430">
-        <v>2162706</v>
+        <v>2162714</v>
       </c>
       <c r="E430">
         <v>2488464</v>
@@ -7684,10 +7684,10 @@
         <v>2635038</v>
       </c>
       <c r="D431">
-        <v>5486728</v>
+        <v>5487356</v>
       </c>
       <c r="E431">
-        <v>6460441</v>
+        <v>6462416</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -7701,7 +7701,7 @@
         <v>3135952</v>
       </c>
       <c r="D432">
-        <v>6576391</v>
+        <v>6576417</v>
       </c>
       <c r="E432">
         <v>7593005</v>
@@ -7718,7 +7718,7 @@
         <v>647422</v>
       </c>
       <c r="D433">
-        <v>1588927</v>
+        <v>1588933</v>
       </c>
       <c r="E433">
         <v>3509372</v>
@@ -7735,7 +7735,7 @@
         <v>519985</v>
       </c>
       <c r="D434">
-        <v>1445056</v>
+        <v>1445057</v>
       </c>
       <c r="E434">
         <v>1956612</v>
@@ -7752,7 +7752,7 @@
         <v>485567</v>
       </c>
       <c r="D435">
-        <v>1059284</v>
+        <v>1059289</v>
       </c>
       <c r="E435">
         <v>1339942</v>
@@ -7769,10 +7769,10 @@
         <v>1055525</v>
       </c>
       <c r="D436">
-        <v>2565887</v>
+        <v>2565911</v>
       </c>
       <c r="E436">
-        <v>3815108</v>
+        <v>3815464</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -7786,10 +7786,10 @@
         <v>946105</v>
       </c>
       <c r="D437">
-        <v>2594592</v>
+        <v>2594595</v>
       </c>
       <c r="E437">
-        <v>3830011</v>
+        <v>3830049</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -7803,10 +7803,10 @@
         <v>880097</v>
       </c>
       <c r="D438">
-        <v>2098996</v>
+        <v>2098998</v>
       </c>
       <c r="E438">
-        <v>1984222</v>
+        <v>1984242</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -7820,10 +7820,10 @@
         <v>297033</v>
       </c>
       <c r="D439">
-        <v>903734</v>
+        <v>903735</v>
       </c>
       <c r="E439">
-        <v>1984222</v>
+        <v>1984242</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -7837,10 +7837,10 @@
         <v>781086</v>
       </c>
       <c r="D440">
-        <v>1720011</v>
+        <v>1720013</v>
       </c>
       <c r="E440">
-        <v>1568920</v>
+        <v>1568936</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -7854,10 +7854,10 @@
         <v>242027</v>
       </c>
       <c r="D441">
-        <v>583054</v>
+        <v>583055</v>
       </c>
       <c r="E441">
-        <v>784460</v>
+        <v>784468</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -7871,10 +7871,10 @@
         <v>255320</v>
       </c>
       <c r="D442">
-        <v>656661</v>
+        <v>656663</v>
       </c>
       <c r="E442">
-        <v>1034500</v>
+        <v>1034540</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -7888,10 +7888,10 @@
         <v>297033</v>
       </c>
       <c r="D443">
-        <v>699665</v>
+        <v>699666</v>
       </c>
       <c r="E443">
-        <v>784460</v>
+        <v>784468</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -7905,10 +7905,10 @@
         <v>374041</v>
       </c>
       <c r="D444">
-        <v>816276</v>
+        <v>816277</v>
       </c>
       <c r="E444">
-        <v>784460</v>
+        <v>784468</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -7939,10 +7939,10 @@
         <v>165018</v>
       </c>
       <c r="D446">
-        <v>408138</v>
+        <v>408139</v>
       </c>
       <c r="E446">
-        <v>738315</v>
+        <v>738323</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -7973,10 +7973,10 @@
         <v>234551</v>
       </c>
       <c r="D448">
-        <v>427908</v>
+        <v>427912</v>
       </c>
       <c r="E448">
-        <v>778153</v>
+        <v>778178</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -7990,10 +7990,10 @@
         <v>1817768</v>
       </c>
       <c r="D449">
-        <v>3102330</v>
+        <v>3102359</v>
       </c>
       <c r="E449">
-        <v>3395575</v>
+        <v>3395685</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -8007,10 +8007,10 @@
         <v>703652</v>
       </c>
       <c r="D450">
-        <v>1230234</v>
+        <v>1230246</v>
       </c>
       <c r="E450">
-        <v>1910011</v>
+        <v>1910073</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -8024,10 +8024,10 @@
         <v>1495261</v>
       </c>
       <c r="D451">
-        <v>3155818</v>
+        <v>3155848</v>
       </c>
       <c r="E451">
-        <v>5447069</v>
+        <v>5447244</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -8041,10 +8041,10 @@
         <v>1348667</v>
       </c>
       <c r="D452">
-        <v>2727911</v>
+        <v>2727937</v>
       </c>
       <c r="E452">
-        <v>4881139</v>
+        <v>4881297</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -8058,10 +8058,10 @@
         <v>1114116</v>
       </c>
       <c r="D453">
-        <v>2727911</v>
+        <v>2727937</v>
       </c>
       <c r="E453">
-        <v>7074115</v>
+        <v>7074343</v>
       </c>
     </row>
     <row r="454" spans="1:5">
@@ -8072,13 +8072,13 @@
         <v>815257</v>
       </c>
       <c r="C454">
-        <v>1174373</v>
+        <v>1174376</v>
       </c>
       <c r="D454">
-        <v>2318260</v>
+        <v>2318274</v>
       </c>
       <c r="E454">
-        <v>3398046</v>
+        <v>3398147</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -8089,13 +8089,13 @@
         <v>407628</v>
       </c>
       <c r="C455">
-        <v>527270</v>
+        <v>527271</v>
       </c>
       <c r="D455">
-        <v>1183792</v>
+        <v>1183800</v>
       </c>
       <c r="E455">
-        <v>2174750</v>
+        <v>2174814</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -8106,13 +8106,13 @@
         <v>468018</v>
       </c>
       <c r="C456">
-        <v>719004</v>
+        <v>719006</v>
       </c>
       <c r="D456">
-        <v>1677039</v>
+        <v>1677049</v>
       </c>
       <c r="E456">
-        <v>3126203</v>
+        <v>3126295</v>
       </c>
     </row>
     <row r="457" spans="1:5">
@@ -8123,13 +8123,13 @@
         <v>120779</v>
       </c>
       <c r="C457">
-        <v>191734</v>
+        <v>191735</v>
       </c>
       <c r="D457">
-        <v>443922</v>
+        <v>443925</v>
       </c>
       <c r="E457">
-        <v>543687</v>
+        <v>543704</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -8140,13 +8140,13 @@
         <v>588796</v>
       </c>
       <c r="C458">
-        <v>1246273</v>
+        <v>1246277</v>
       </c>
       <c r="D458">
-        <v>2466234</v>
+        <v>2466249</v>
       </c>
       <c r="E458">
-        <v>2446593</v>
+        <v>2446666</v>
       </c>
     </row>
     <row r="459" spans="1:5">
@@ -8157,13 +8157,13 @@
         <v>256655</v>
       </c>
       <c r="C459">
-        <v>431402</v>
+        <v>431404</v>
       </c>
       <c r="D459">
-        <v>937169</v>
+        <v>937175</v>
       </c>
       <c r="E459">
-        <v>1291258</v>
+        <v>1291296</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -8174,13 +8174,13 @@
         <v>603894</v>
       </c>
       <c r="C460">
-        <v>1150406</v>
+        <v>1150409</v>
       </c>
       <c r="D460">
-        <v>2022312</v>
+        <v>2022324</v>
       </c>
       <c r="E460">
-        <v>1699023</v>
+        <v>1699074</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -8191,13 +8191,13 @@
         <v>618991</v>
       </c>
       <c r="C461">
-        <v>1102473</v>
+        <v>1102476</v>
       </c>
       <c r="D461">
-        <v>2318260</v>
+        <v>2318274</v>
       </c>
       <c r="E461">
-        <v>2990281</v>
+        <v>2990369</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -8208,13 +8208,13 @@
         <v>120779</v>
       </c>
       <c r="C462">
-        <v>191734</v>
+        <v>191735</v>
       </c>
       <c r="D462">
-        <v>394597</v>
+        <v>394600</v>
       </c>
       <c r="E462">
-        <v>543687</v>
+        <v>543704</v>
       </c>
     </row>
     <row r="463" spans="1:5">
@@ -8228,10 +8228,10 @@
         <v>1385078</v>
       </c>
       <c r="D463">
-        <v>2883828</v>
+        <v>2883839</v>
       </c>
       <c r="E463">
-        <v>3626378</v>
+        <v>3626627</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -8245,10 +8245,10 @@
         <v>1259162</v>
       </c>
       <c r="D464">
-        <v>2792278</v>
+        <v>2792289</v>
       </c>
       <c r="E464">
-        <v>3432108</v>
+        <v>3432344</v>
       </c>
     </row>
     <row r="465" spans="1:5">
@@ -8282,7 +8282,7 @@
         <v>1425878</v>
       </c>
       <c r="E466">
-        <v>1713378</v>
+        <v>1713437</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -8296,10 +8296,10 @@
         <v>566623</v>
       </c>
       <c r="D467">
-        <v>1281701</v>
+        <v>1281706</v>
       </c>
       <c r="E467">
-        <v>1489405</v>
+        <v>1489508</v>
       </c>
     </row>
     <row r="468" spans="1:5">
@@ -8313,10 +8313,10 @@
         <v>615696</v>
       </c>
       <c r="D468">
-        <v>1337211</v>
+        <v>1337224</v>
       </c>
       <c r="E468">
-        <v>3820022</v>
+        <v>3820145</v>
       </c>
     </row>
     <row r="469" spans="1:5">
@@ -8330,10 +8330,10 @@
         <v>527739</v>
       </c>
       <c r="D469">
-        <v>1123257</v>
+        <v>1123268</v>
       </c>
       <c r="E469">
-        <v>2688164</v>
+        <v>2688251</v>
       </c>
     </row>
     <row r="470" spans="1:5">
@@ -8347,10 +8347,10 @@
         <v>908884</v>
       </c>
       <c r="D470">
-        <v>1765119</v>
+        <v>1765135</v>
       </c>
       <c r="E470">
-        <v>3607799</v>
+        <v>3607915</v>
       </c>
     </row>
     <row r="471" spans="1:5">
@@ -8364,10 +8364,10 @@
         <v>209860</v>
       </c>
       <c r="D471">
-        <v>503526</v>
+        <v>503527</v>
       </c>
       <c r="E471">
-        <v>841838</v>
+        <v>841896</v>
       </c>
     </row>
     <row r="472" spans="1:5">
@@ -8378,13 +8378,13 @@
         <v>166071</v>
       </c>
       <c r="C472">
-        <v>239668</v>
+        <v>239669</v>
       </c>
       <c r="D472">
-        <v>542572</v>
+        <v>542575</v>
       </c>
       <c r="E472">
-        <v>883492</v>
+        <v>883518</v>
       </c>
     </row>
     <row r="473" spans="1:5">
@@ -8398,10 +8398,10 @@
         <v>298852</v>
       </c>
       <c r="D473">
-        <v>767780</v>
+        <v>767781</v>
       </c>
       <c r="E473">
-        <v>1215946</v>
+        <v>1215987</v>
       </c>
     </row>
     <row r="474" spans="1:5">
@@ -8415,10 +8415,10 @@
         <v>777016</v>
       </c>
       <c r="D474">
-        <v>1974292</v>
+        <v>1974293</v>
       </c>
       <c r="E474">
-        <v>2874054</v>
+        <v>2874152</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -8432,10 +8432,10 @@
         <v>668994</v>
       </c>
       <c r="D475">
-        <v>1710592</v>
+        <v>1710607</v>
       </c>
       <c r="E475">
-        <v>2805226</v>
+        <v>2805489</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -8449,10 +8449,10 @@
         <v>1017198</v>
       </c>
       <c r="D476">
-        <v>2642894</v>
+        <v>2642927</v>
       </c>
       <c r="E476">
-        <v>3913068</v>
+        <v>3913351</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -8466,10 +8466,10 @@
         <v>292619</v>
       </c>
       <c r="D477">
-        <v>868897</v>
+        <v>868908</v>
       </c>
       <c r="E477">
-        <v>1212500</v>
+        <v>1212588</v>
       </c>
     </row>
     <row r="478" spans="1:5">
@@ -8480,13 +8480,13 @@
         <v>1316232</v>
       </c>
       <c r="C478">
-        <v>2370134</v>
+        <v>2370144</v>
       </c>
       <c r="D478">
-        <v>5385176</v>
+        <v>5386038</v>
       </c>
       <c r="E478">
-        <v>5548986</v>
+        <v>5550711</v>
       </c>
     </row>
     <row r="479" spans="1:5">
@@ -8500,10 +8500,10 @@
         <v>343235</v>
       </c>
       <c r="D479">
-        <v>836736</v>
+        <v>836738</v>
       </c>
       <c r="E479">
-        <v>1043749</v>
+        <v>1043776</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -8517,7 +8517,7 @@
         <v>281577</v>
       </c>
       <c r="D480">
-        <v>769270</v>
+        <v>769274</v>
       </c>
       <c r="E480">
         <v>1465377</v>
@@ -8531,13 +8531,13 @@
         <v>3160811</v>
       </c>
       <c r="C481">
-        <v>5543702</v>
+        <v>5543728</v>
       </c>
       <c r="D481">
-        <v>11874145</v>
+        <v>11876047</v>
       </c>
       <c r="E481">
-        <v>11046112</v>
+        <v>11049547</v>
       </c>
     </row>
     <row r="482" spans="1:5">
@@ -8548,13 +8548,13 @@
         <v>1186463</v>
       </c>
       <c r="C482">
-        <v>1928244</v>
+        <v>1928253</v>
       </c>
       <c r="D482">
-        <v>4883451</v>
+        <v>4884234</v>
       </c>
       <c r="E482">
-        <v>6897338</v>
+        <v>6899482</v>
       </c>
     </row>
     <row r="483" spans="1:5">
@@ -8565,13 +8565,13 @@
         <v>2224618</v>
       </c>
       <c r="C483">
-        <v>3320865</v>
+        <v>3320880</v>
       </c>
       <c r="D483">
-        <v>7726556</v>
+        <v>7727794</v>
       </c>
       <c r="E483">
-        <v>10060779</v>
+        <v>10063907</v>
       </c>
     </row>
     <row r="484" spans="1:5">
@@ -8582,13 +8582,13 @@
         <v>2836388</v>
       </c>
       <c r="C484">
-        <v>4499237</v>
+        <v>4499257</v>
       </c>
       <c r="D484">
-        <v>10971041</v>
+        <v>10972799</v>
       </c>
       <c r="E484">
-        <v>14831869</v>
+        <v>14836481</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -8602,7 +8602,7 @@
         <v>596281</v>
       </c>
       <c r="D485">
-        <v>1740979</v>
+        <v>1740988</v>
       </c>
       <c r="E485">
         <v>4396130</v>
@@ -8619,7 +8619,7 @@
         <v>1962555</v>
       </c>
       <c r="D486">
-        <v>4749909</v>
+        <v>4749925</v>
       </c>
       <c r="E486">
         <v>6128865</v>
@@ -8633,13 +8633,13 @@
         <v>839452</v>
       </c>
       <c r="C487">
-        <v>1228274</v>
+        <v>1228275</v>
       </c>
       <c r="D487">
-        <v>3158201</v>
+        <v>3158208</v>
       </c>
       <c r="E487">
-        <v>5286246</v>
+        <v>5286460</v>
       </c>
     </row>
     <row r="488" spans="1:5">
@@ -8650,13 +8650,13 @@
         <v>1142421</v>
       </c>
       <c r="C488">
-        <v>1978483</v>
+        <v>1978492</v>
       </c>
       <c r="D488">
-        <v>5380840</v>
+        <v>5380896</v>
       </c>
       <c r="E488">
-        <v>8843307</v>
+        <v>8843828</v>
       </c>
     </row>
     <row r="489" spans="1:5">
@@ -8667,13 +8667,13 @@
         <v>203312</v>
       </c>
       <c r="C489">
-        <v>209839</v>
+        <v>209840</v>
       </c>
       <c r="D489">
-        <v>519529</v>
+        <v>519535</v>
       </c>
       <c r="E489">
-        <v>1013882</v>
+        <v>1013942</v>
       </c>
     </row>
     <row r="490" spans="1:5">
@@ -8684,10 +8684,10 @@
         <v>1349252</v>
       </c>
       <c r="C490">
-        <v>2786980</v>
+        <v>2786983</v>
       </c>
       <c r="D490">
-        <v>5149507</v>
+        <v>5149582</v>
       </c>
       <c r="E490">
         <v>4787745</v>
@@ -8704,10 +8704,10 @@
         <v>180352</v>
       </c>
       <c r="D491">
-        <v>369981</v>
+        <v>369986</v>
       </c>
       <c r="E491">
-        <v>428009</v>
+        <v>428064</v>
       </c>
     </row>
     <row r="492" spans="1:5">
@@ -8718,10 +8718,10 @@
         <v>3703267</v>
       </c>
       <c r="C492">
-        <v>7621034</v>
+        <v>7621043</v>
       </c>
       <c r="D492">
-        <v>14632758</v>
+        <v>14632970</v>
       </c>
       <c r="E492">
         <v>14715275</v>
@@ -8735,10 +8735,10 @@
         <v>1492790</v>
       </c>
       <c r="C493">
-        <v>2491018</v>
+        <v>2491021</v>
       </c>
       <c r="D493">
-        <v>5812315</v>
+        <v>5812399</v>
       </c>
       <c r="E493">
         <v>10490794</v>
@@ -8752,10 +8752,10 @@
         <v>3789389</v>
       </c>
       <c r="C494">
-        <v>6609829</v>
+        <v>6609837</v>
       </c>
       <c r="D494">
-        <v>13001231</v>
+        <v>13001419</v>
       </c>
       <c r="E494">
         <v>16053027</v>
@@ -8772,10 +8772,10 @@
         <v>26945</v>
       </c>
       <c r="D495">
-        <v>54784</v>
+        <v>54791</v>
       </c>
       <c r="E495">
-        <v>72941</v>
+        <v>72959</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -8789,10 +8789,10 @@
         <v>29928</v>
       </c>
       <c r="D496">
-        <v>57284</v>
+        <v>57289</v>
       </c>
       <c r="E496">
-        <v>74677</v>
+        <v>74696</v>
       </c>
     </row>
     <row r="497" spans="1:5">
@@ -8803,13 +8803,13 @@
         <v>916213</v>
       </c>
       <c r="C497">
-        <v>1589727</v>
+        <v>1589747</v>
       </c>
       <c r="D497">
-        <v>3177448</v>
+        <v>3177898</v>
       </c>
       <c r="E497">
-        <v>4376477</v>
+        <v>4377519</v>
       </c>
     </row>
     <row r="498" spans="1:5">
@@ -8820,13 +8820,13 @@
         <v>4134485</v>
       </c>
       <c r="C498">
-        <v>7611532</v>
+        <v>7611562</v>
       </c>
       <c r="D498">
-        <v>14530291</v>
+        <v>14531411</v>
       </c>
       <c r="E498">
-        <v>16960274</v>
+        <v>16964086</v>
       </c>
     </row>
     <row r="499" spans="1:5">
@@ -8837,13 +8837,13 @@
         <v>640067</v>
       </c>
       <c r="C499">
-        <v>1051775</v>
+        <v>1051780</v>
       </c>
       <c r="D499">
-        <v>2211131</v>
+        <v>2211302</v>
       </c>
       <c r="E499">
-        <v>3559564</v>
+        <v>3560364</v>
       </c>
     </row>
     <row r="500" spans="1:5">
@@ -8854,13 +8854,13 @@
         <v>294085</v>
       </c>
       <c r="C500">
-        <v>553566</v>
+        <v>553568</v>
       </c>
       <c r="D500">
-        <v>1052920</v>
+        <v>1053001</v>
       </c>
       <c r="E500">
-        <v>1326112</v>
+        <v>1326410</v>
       </c>
     </row>
     <row r="501" spans="1:5">
@@ -8874,10 +8874,10 @@
         <v>2326570</v>
       </c>
       <c r="D501">
-        <v>5818015</v>
+        <v>5818061</v>
       </c>
       <c r="E501">
-        <v>9259953</v>
+        <v>9260606</v>
       </c>
     </row>
   </sheetData>
